--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -92,12 +92,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008CC53F"/>
+        <fgColor rgb="00F4B942"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B942"/>
+        <fgColor rgb="008CC53F"/>
       </patternFill>
     </fill>
     <fill>
@@ -672,7 +672,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>KD 8. The #1 buyer question and a prime AI-overview answer target. Pillar anchor.</t>
+          <t>KD 8. The #1 buyer question and a prime AI-overview target. Pillar anchor.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>KD 10. High-intent decision query AI engines love to answer.</t>
+          <t>KD 10. High-intent decision query AI engines answer directly.</t>
         </is>
       </c>
     </row>
@@ -731,23 +731,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Do Matchmakers Actually Work? What to Expect</t>
+          <t>What Is Matchmaking, and How Does It Work Today?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>do matchmakers work</t>
+          <t>what is matchmaking</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>KD 23. Objection-handling content, strong citation magnet.</t>
+          <t>KD 32. Definitional head term that owns the AI snippet.</t>
         </is>
       </c>
     </row>
@@ -780,23 +780,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What Is Matchmaking? How Modern Matchmaking Works</t>
+          <t>How to Choose a Matchmaker You Can Actually Trust</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>what is matchmaking</t>
+          <t>hire a matchmaker</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>KD 32. Definitional head term — owns the AI-overview snippet.</t>
+          <t>KD 23. Bottom-of-research decision query.</t>
         </is>
       </c>
     </row>
@@ -829,21 +829,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How to Find a Matchmaker You Can Trust</t>
+          <t>Matchmaker vs Online Dating: Which Actually Gets You There?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>hire a matchmaker</t>
+          <t>matchmaker vs online dating</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -868,7 +868,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>KD 23. Bottom-of-research decision query.</t>
+          <t>Comparison content separating you from the apps.</t>
         </is>
       </c>
     </row>
@@ -878,23 +878,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Professional Matchmaker Cost: What You're Really Paying For</t>
+          <t>Are Matchmakers Still a Thing in 2026?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>professional matchmaker cost</t>
+          <t>are matchmakers still a thing</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
         <v>70</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>31</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>KD 10. Commercial cost query, easy win.</t>
+          <t>KD 31. Curiosity query that reframes the category.</t>
         </is>
       </c>
     </row>
@@ -927,38 +927,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Matchmaker vs Online Dating: Which Is Right for You?</t>
+          <t>Date Ideas in Chicago Locals Swear By</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>matchmaker vs online dating</t>
+          <t>date ideas chicago</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>320</v>
+        <v>2400</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>18</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Comparison content separating you from apps.</t>
+          <t>KD 18, 2,400 vol. Highest-volume local term in the set.</t>
         </is>
       </c>
     </row>
@@ -976,28 +976,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Are Matchmakers Still a Thing in 2026?</t>
+          <t>Atlanta Date Nights Worth Getting Dressed For</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>are matchmakers still a thing</t>
+          <t>date night ideas atlanta</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>70</v>
+        <v>1600</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>16</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>KD 31. Curiosity query, reframes the category.</t>
+          <t>KD 16, 1,600 vol.</t>
         </is>
       </c>
     </row>
@@ -1025,19 +1025,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Best Date Night Ideas in Dallas</t>
+          <t>Where to Take a Date in Phoenix</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>date night in dallas ideas</t>
+          <t>date ideas phoenix</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1600</v>
+        <v>880</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>KD 6. Lowest-difficulty local term in the set.</t>
+          <t>KD 9. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1074,19 +1074,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Romantic &amp; Fun Date Ideas in Phoenix</t>
+          <t>Fort Worth After Dark: Date Nights Worth the Drive</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>date ideas phoenix</t>
+          <t>date night ideas fort worth</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>880</v>
+        <v>720</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>KD 9. Easy local win, no current ranking.</t>
+          <t>KD 7. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1123,19 +1123,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Fort Worth</t>
+          <t>Philadelphia Date Nights, From Classic to Unexpected</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>date night ideas fort worth</t>
+          <t>date night ideas philadelphia</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
         <v>720</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>KD 7. Easy local win.</t>
+          <t>KD 9. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1172,19 +1172,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Creative Date Night Ideas in Philadelphia</t>
+          <t>Date Night in Las Vegas, Beyond the Strip</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>date night ideas philadelphia</t>
+          <t>date night ideas las vegas</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
         <v>720</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>KD 9. Easy local win.</t>
+          <t>KD 10. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1221,19 +1221,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chicago Date Ideas Locals Actually Love</t>
+          <t>The Best Date Ideas in Boston, Season by Season</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>chicago date ideas</t>
+          <t>date ideas boston</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>720</v>
+        <v>1300</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>KD 9. 720 vol, very low difficulty.</t>
+          <t>KD 13, 1,300 vol.</t>
         </is>
       </c>
     </row>
@@ -1270,19 +1270,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Best Date Ideas in Denver</t>
+          <t>A Local's Shortlist of LA Date Ideas</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>date ideas denver</t>
+          <t>date ideas los angeles</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>720</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>KD 11. Easy local win.</t>
+          <t>KD 12, 1,300 vol.</t>
         </is>
       </c>
     </row>
@@ -1319,19 +1319,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Date Ideas in Los Angeles: A Local's Guide</t>
+          <t>Rain or Shine: Date Ideas in Seattle</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>date ideas los angeles</t>
+          <t>date ideas seattle</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>KD 12. 1,300 vol.</t>
+          <t>KD 16, 1,000 vol.</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Date Ideas in Philadelphia: Where to Go</t>
+          <t>The Best Date Ideas in Portland</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>date ideas philadelphia</t>
+          <t>date ideas portland</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
         <v>720</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>KD 11. Easy local win.</t>
+          <t>KD 15. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1417,19 +1417,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fun Date Night Ideas in Las Vegas</t>
+          <t>Date Ideas in San Francisco for Every Kind of Couple</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>date night ideas las vegas</t>
+          <t>date ideas san francisco</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>KD 10. Easy local win.</t>
+          <t>KD 8. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1466,19 +1466,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Best Date Ideas in Boston</t>
+          <t>Date Ideas in Nashville for Music City Romance</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>date ideas boston</t>
+          <t>date ideas nashville tennessee</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1300</v>
+        <v>590</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>KD 13. 1,300 vol.</t>
+          <t>KD 7. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1515,19 +1515,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Phoenix for Every Season</t>
+          <t>Austin Date Ideas, From Honky-Tonks to Hidden Patios</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>date night ideas phoenix</t>
+          <t>austin date ideas</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>880</v>
+        <v>590</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>KD 14. Easy local win.</t>
+          <t>KD 5. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1564,19 +1564,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Denver</t>
+          <t>Cincinnati Date Nights, Riverfront and Beyond</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>date night denver</t>
+          <t>date night cincinnati</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>KD 14. Easy local win.</t>
+          <t>KD 7. Easy local win.</t>
         </is>
       </c>
     </row>
@@ -1613,38 +1613,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Best Date Ideas in Seattle</t>
+          <t>How to Find a Matchmaker Near You</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>date ideas seattle</t>
+          <t>matchmaker near me</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+        <v>24</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>KD 16. 1,000 vol.</t>
+          <t>KD 24, 2,400 vol. You rank #13 — striking distance. Core local anchor.</t>
         </is>
       </c>
     </row>
@@ -1662,38 +1662,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Romantic Date Ideas in San Antonio</t>
+          <t>San Francisco Matchmaking, Done for You</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>date ideas san antonio</t>
+          <t>san francisco matchmaker</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>880</v>
+        <v>110</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>KD 19. Easy local win.</t>
+          <t>KD 6. Commercial money page, near-zero difficulty.</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sacramento Matchmaker: Personalized Matchmaking in Sacramento</t>
+          <t>Meet Your Match in Sacramento</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>KD 6. New-metro money page, near-zero difficulty.</t>
+          <t>KD 6. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -1760,19 +1760,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>San Francisco Matchmaker: Bay Area Introductions</t>
+          <t>A Personal Matchmaker for New Jersey Singles</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>san francisco matchmaker</t>
+          <t>new jersey matchmaker</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>KD 6. Commercial, KD 6 — fast win.</t>
+          <t>KD 5. New-area money page.</t>
         </is>
       </c>
     </row>
@@ -1809,19 +1809,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Jersey Matchmaker: Statewide Matchmaking</t>
+          <t>Matchmaking for Gay Singles in Los Angeles</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>new jersey matchmaker</t>
+          <t>gay matchmaker los angeles</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>KD 5. New-area money page.</t>
+          <t>KD 3. Niche-local page, near-zero difficulty.</t>
         </is>
       </c>
     </row>
@@ -1858,23 +1858,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pittsburgh Matchmaker: Meet Someone Worth Your Time</t>
+          <t>Find Love in Tucson Without the Apps</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>pittsburgh matchmaker</t>
+          <t>matchmaker tucson</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>5</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>KD 29. New-metro money page.</t>
+          <t>KD 5. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -1907,23 +1907,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Professional Matchmaker in NYC: How It Works</t>
+          <t>Your Personal Matchmaker in Memphis</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>professional matchmaker nyc</t>
+          <t>matchmaker memphis</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>2</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>KD 29. High-intent NYC commercial term.</t>
+          <t>KD 2. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -1956,23 +1956,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Charlotte Matchmaker: Curated Introductions in NC</t>
+          <t>Matchmaking in Reno, the Personal Way</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>matchmaker charlotte nc</t>
+          <t>reno matchmaker</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>8</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>KD 27. New-metro money page.</t>
+          <t>Estimated vol — new-metro money page (Reno is high-local-keyword).</t>
         </is>
       </c>
     </row>
@@ -2005,19 +2005,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Elite Matchmaking in NYC for Discerning Singles</t>
+          <t>Introductions for Tulsa Singles</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>elite matchmaking nyc</t>
+          <t>tulsa matchmaker</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>KD 4. Luxury positioning, near-zero KD.</t>
+          <t>KD 17. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -2054,23 +2054,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Matchmaker Near Me: How to Find a Local Matchmaker</t>
+          <t>Meet Quality Singles in Omaha</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>matchmaker near me</t>
+          <t>omaha matchmaker</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2400</v>
+        <v>30</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>20</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>KD 24, 2,400 vol. You rank #13 — striking distance. Core local anchor.</t>
+          <t>KD 20. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       <c r="E32" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2152,23 +2152,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>First Date Tips From Professional Matchmakers</t>
+          <t>The Best Questions to Ask on a First Date</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>first date tips</t>
+          <t>good questions to ask on a first date</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>KD 34, 1,600 vol.</t>
+          <t>KD 30, 1,300 vol.</t>
         </is>
       </c>
     </row>
@@ -2201,21 +2201,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>How to Date With Intention in Your 30s, 40s and Beyond</t>
+          <t>Funny First-Date Questions to Break the Ice</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>how to date</t>
+          <t>funny first date questions</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1600</v>
+        <v>720</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>KD 25, 1,600 vol.</t>
+          <t>KD 22, 720 vol. Humor angle.</t>
         </is>
       </c>
     </row>
@@ -2250,23 +2250,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Good Questions to Ask on a First Date</t>
+          <t>First-Date Tips From Matchmakers Who've Seen It All</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>good questions to ask on a first date</t>
+          <t>first date tips</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>KD 30, 1,300 vol.</t>
+          <t>KD 34, 1,600 vol.</t>
         </is>
       </c>
     </row>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Ideal First Date: What Matchmakers Recommend</t>
+          <t>What to Wear on a First Date, Decoded</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ideal first date</t>
+          <t>what should i wear on a first date</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1300</v>
+        <v>260</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>KD 29, 1,300 vol.</t>
+          <t>KD 23. Style angle.</t>
         </is>
       </c>
     </row>
@@ -2348,21 +2348,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Best First Dates: Ideas That Lead to a Second</t>
+          <t>Should You Bring Flowers on a First Date?</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>best first dates</t>
+          <t>should i bring flowers on a first date</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>KD 23, 1,000 vol.</t>
+          <t>KD 22. Etiquette angle.</t>
         </is>
       </c>
     </row>
@@ -2397,21 +2397,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>First Date Conversation Starters That Aren't Boring</t>
+          <t>What Makes a Great First Date</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>first date conversation starters</t>
+          <t>best first dates</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>KD 27, 1,000 vol.</t>
+          <t>KD 23, 1,000 vol.</t>
         </is>
       </c>
     </row>
@@ -2446,21 +2446,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What to Wear on a First Date: A Style Guide</t>
+          <t>How to Date With Intention at Any Age</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>what should i wear on a first date</t>
+          <t>how to date</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>260</v>
+        <v>1600</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>KD 23, 260 vol.</t>
+          <t>KD 25, 1,600 vol.</t>
         </is>
       </c>
     </row>
@@ -2495,21 +2495,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Should You Bring Flowers on a First Date?</t>
+          <t>Luxury Dating: What Discreet, High-End Matchmaking Looks Like</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>should i bring flowers on a first date</t>
+          <t>luxury dating</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>170</v>
+        <v>1300</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>KD 22. Easy, oddly high-intent AEO query.</t>
+          <t>KD 28, 1,300 vol. On-brand positioning.</t>
         </is>
       </c>
     </row>
@@ -2544,21 +2544,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Funny First Date Questions to Break the Ice</t>
+          <t>First-Date Red Flags (and the Green Flags to Look For)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>funny first date questions</t>
+          <t>first date red flags</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>KD 22, 720 vol.</t>
+          <t>Estimated — high-share advice topic.</t>
         </is>
       </c>
     </row>
@@ -2593,28 +2593,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Date Ideas in NYC: A Matchmaker's Shortlist</t>
+          <t>How Much Do Matchmakers Make? Inside the Profession</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>date ideas nyc</t>
+          <t>how much do matchmakers make</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1600</v>
+        <v>110</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+        <v>14</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>KD 26, 1,600 vol.</t>
+          <t>KD 14. Curiosity-driven authority builder.</t>
         </is>
       </c>
     </row>
@@ -2642,38 +2642,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Atlanta</t>
+          <t>What to Expect at Your First Matchmaking Consultation</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>date night ideas atlanta</t>
+          <t>matchmaking consultation</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+        <v>22</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>KD 16, 1,600 vol.</t>
+          <t>Estimated — moves prospects toward booking.</t>
         </is>
       </c>
     </row>
@@ -2691,38 +2691,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Houston</t>
+          <t>How Background Checks Make Matchmaking Safer Than Apps</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>date night ideas houston</t>
+          <t>background check dating</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>KD 22, 1,600 vol.</t>
+          <t>Estimated — your verification differentiator.</t>
         </is>
       </c>
     </row>
@@ -2740,38 +2740,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Chicago</t>
+          <t>What Drives the Cost of Matchmaking Services</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>date night ideas chicago</t>
+          <t>matchmaking services cost</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1600</v>
+        <v>170</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+        <v>6</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>KD 21, 1,600 vol.</t>
+          <t>KD 6. Pricing-models angle, distinct from the cost anchor.</t>
         </is>
       </c>
     </row>
@@ -2789,21 +2789,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Date Ideas in Dallas: Beyond Dinner and a Movie</t>
+          <t>The Dallas Date-Night Playbook</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>date ideas dallas</t>
+          <t>date night ideas dallas</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>KD 23, 1,600 vol.</t>
+          <t>KD 23, 1,900 vol.</t>
         </is>
       </c>
     </row>
@@ -2838,23 +2838,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Boston</t>
+          <t>A Matchmaker's Shortlist of NYC Date Ideas</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>date night ideas boston</t>
+          <t>date ideas nyc</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>26</v>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>KD 17, 1,300 vol.</t>
+          <t>KD 26, 1,600 vol.</t>
         </is>
       </c>
     </row>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Date Ideas in Houston for Couples</t>
+          <t>The Houston Date-Night Guide</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>date ideas houston</t>
+          <t>date night ideas houston</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>KD 22, 1,300 vol.</t>
+          <t>KD 22, 1,600 vol.</t>
         </is>
       </c>
     </row>
@@ -2936,23 +2936,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Date Ideas in Atlanta You Haven't Tried</t>
+          <t>A Denver Date-Night Guide for Couples</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>date ideas atlanta</t>
+          <t>date night ideas denver</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
         <v>880</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>19</v>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>KD 26, 880 vol.</t>
+          <t>KD 19, 880 vol.</t>
         </is>
       </c>
     </row>
@@ -2985,19 +2985,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Date Night in Orlando: Romantic Spots</t>
+          <t>Date Ideas in San Antonio Beyond the Riverwalk</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>date night orlando</t>
+          <t>date ideas san antonio</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>KD 18, 1,000 vol.</t>
+          <t>KD 19, 880 vol.</t>
         </is>
       </c>
     </row>
@@ -3034,23 +3034,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Portland</t>
+          <t>Where to Take a Date in St. Louis</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>date ideas portland</t>
+          <t>date ideas st louis</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
         <v>720</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>22</v>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>KD 15, 720 vol.</t>
+          <t>KD 22, 720 vol.</t>
         </is>
       </c>
     </row>
@@ -3083,23 +3083,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Date Ideas in St. Louis</t>
+          <t>Date Night in Colorado Springs</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>date ideas st louis</t>
+          <t>date night colorado springs</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
         <v>720</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>18</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>KD 22, 720 vol.</t>
+          <t>KD 18, 720 vol.</t>
         </is>
       </c>
     </row>
@@ -3132,16 +3132,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Colorado Springs</t>
+          <t>Romantic Date Nights in Orlando</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>date night colorado springs</t>
+          <t>date night orlando</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>720</v>
+        <v>1000</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>18</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>KD 18, 720 vol.</t>
+          <t>KD 18, 1,000 vol.</t>
         </is>
       </c>
     </row>
@@ -3181,23 +3181,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fun Date Ideas in NYC for Every Budget</t>
+          <t>Date Night in Tampa, From Bayshore to Ybor</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>fun date ideas nyc</t>
+          <t>date night ideas tampa</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>12</v>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>KD 22, 1,000 vol.</t>
+          <t>KD 12, 480 vol.</t>
         </is>
       </c>
     </row>
@@ -3230,23 +3230,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Date Night in Houston: Where Locals Go</t>
+          <t>Miami Date Nights, From South Beach to Wynwood</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>date night houston</t>
+          <t>date night ideas miami</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>10</v>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>KD 25, 1,000 vol.</t>
+          <t>KD 10, 390 vol.</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jewish Matchmaker in NYC: Modern Matchmaking, Timeless Tradition</t>
+          <t>Date Night in Jacksonville by the Water</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>jewish matchmaker nyc</t>
+          <t>date night jacksonville fl</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>110</v>
+        <v>480</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>15</v>
@@ -3298,19 +3298,19 @@
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>KD 15. Niche-local money page.</t>
+          <t>KD 15, 480 vol.</t>
         </is>
       </c>
     </row>
@@ -3328,38 +3328,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gay Matchmaker in Los Angeles</t>
+          <t>Where to Take a Date in Sacramento</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>gay matchmaker los angeles</t>
+          <t>date ideas sacramento</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>110</v>
+        <v>590</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>25</v>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>KD 3. Near-zero difficulty niche page.</t>
+          <t>KD 25, 590 vol.</t>
         </is>
       </c>
     </row>
@@ -3377,38 +3377,38 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gay Matchmaker in NYC</t>
+          <t>Date Ideas in Baltimore Beyond the Inner Harbor</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>gay matchmaker nyc</t>
+          <t>date ideas baltimore</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>90</v>
+        <v>390</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>21</v>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>KD 14. Niche-local money page.</t>
+          <t>KD 21, 390 vol.</t>
         </is>
       </c>
     </row>
@@ -3426,23 +3426,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Matchmaking in New York City: A Complete Guide</t>
+          <t>Dating in Pittsburgh? Let a Matchmaker Do the Hard Part</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>matchmaking new york city</t>
+          <t>pittsburgh matchmaker</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>KD 31, 390 vol.</t>
+          <t>KD 29. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3475,23 +3475,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Elite Matchmaker in New York</t>
+          <t>Curated Introductions for Charlotte Singles</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>elite matchmaker new york</t>
+          <t>matchmaker charlotte nc</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>27</v>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>KD 12. Luxury-local page.</t>
+          <t>KD 27. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3524,23 +3524,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Christian Matchmaker Near You</t>
+          <t>A Complete Guide to Matchmaking in New York City</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>christian matchmaker near me</t>
+          <t>matchmaking new york city</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>70</v>
+        <v>390</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>KD 24. Faith-based niche page.</t>
+          <t>KD 31, 390 vol.</t>
         </is>
       </c>
     </row>
@@ -3573,19 +3573,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Matchmaker in Pittsburgh, PA</t>
+          <t>Modern Jewish Matchmaking in New York</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>matchmaker pittsburgh pa</t>
+          <t>jewish matchmaker nyc</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>KD 17. New-metro money page.</t>
+          <t>KD 15. Niche-local money page.</t>
         </is>
       </c>
     </row>
@@ -3622,19 +3622,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Matchmaker Cost in NYC: What to Expect</t>
+          <t>High-End Introductions With a Miami Matchmaker</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>matchmaker nyc cost</t>
+          <t>millionaire matchmaker miami</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -3648,12 +3648,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>KD 9. Local commercial-cost page.</t>
+          <t>KD 13. Luxury-local page.</t>
         </is>
       </c>
     </row>
@@ -3671,19 +3671,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tulsa Matchmaker: Introductions in Tulsa</t>
+          <t>Matchmaking in New Orleans, the Personal Way</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>tulsa matchmaker</t>
+          <t>new orleans matchmaker</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>Estimated vol — new-metro money page (Tulsa is a high-local-keyword metro in the set).</t>
+          <t>KD 9. New-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3720,19 +3720,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Omaha Matchmaker: Meet Quality Singles in Omaha</t>
+          <t>Meet Your Match in Cleveland</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>omaha matchmaker</t>
+          <t>cleveland matchmaker</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Estimated vol — new-metro money page.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3769,19 +3769,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New Orleans Matchmaker: Curated Introductions</t>
+          <t>A Personal Matchmaker for Columbus Singles</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>new orleans matchmaker</t>
+          <t>columbus matchmaker</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>Estimated vol — new-metro money page.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3818,19 +3818,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cincinnati Matchmaker</t>
+          <t>Detroit Matchmaking, Handled for You</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>cincinnati matchmaker</t>
+          <t>detroit matchmaker</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
         <v>500</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Estimated vol — new-metro money page.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3867,38 +3867,38 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dating in Your 30s: A Practical Guide</t>
+          <t>Find Love in Baltimore Without the Apps</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>dating in your 30s</t>
+          <t>baltimore matchmaker</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>16</v>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>KD 31, 720 vol.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3916,38 +3916,38 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>First Date Topics to Talk About When Conversation Stalls</t>
+          <t>How Matchmaking Works in Raleigh-Durham</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>first date topics to talk about</t>
+          <t>raleigh matchmaker</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>14</v>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>KD 41, 1,300 vol.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -3965,38 +3965,38 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Great First Date Questions to Really Get to Know Someone</t>
+          <t>Your Cincinnati Matchmaker, Introductions Done Right</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>great first date questions</t>
+          <t>cincinnati matchmaker</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>14</v>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>KD 35, 1,300 vol.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -4014,21 +4014,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cool First Date Questions That Spark Real Conversation</t>
+          <t>What Does a Relationship Coach Really Do?</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>cool first date questions</t>
+          <t>relationship coach</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>1900</v>
+        <v>6600</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>KD 38, 1,900 vol.</t>
+          <t>KD 39, 6,600 vol. Big pillar term.</t>
         </is>
       </c>
     </row>
@@ -4063,21 +4063,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>First Date Advice From Matchmakers Who've Seen It All</t>
+          <t>What a Dating Coach Actually Changes for Men</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>first date advice</t>
+          <t>dating coach for men</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>880</v>
+        <v>720</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>KD 32, 880 vol.</t>
+          <t>KD 39, 720 vol.</t>
         </is>
       </c>
     </row>
@@ -4112,23 +4112,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What to Ask on a First Date Without an Interrogation</t>
+          <t>Second-Date Ideas That Build Momentum</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>what to ask on a first date</t>
+          <t>second date ideas</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>KD 32, 880 vol.</t>
+          <t>Estimated — follow-up to the first-date cluster.</t>
         </is>
       </c>
     </row>
@@ -4161,23 +4161,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dating Coach for Men: What a Coach Actually Changes</t>
+          <t>How to Read Body Language on a Date</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>dating coach for men</t>
+          <t>body language on a date</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>KD 39, 720 vol.</t>
+          <t>Estimated — coaching authority topic.</t>
         </is>
       </c>
     </row>
@@ -4210,23 +4210,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What Does a Relationship Coach Do?</t>
+          <t>Should You Kiss on the First Date?</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>relationship coach</t>
+          <t>first date kiss</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>6600</v>
+        <v>880</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>KD 39, 6,600 vol. Big pillar term.</t>
+          <t>Estimated — common first-date AEO query.</t>
         </is>
       </c>
     </row>
@@ -4259,23 +4259,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>First Date Conversation: Things to Talk About</t>
+          <t>Dating in Your 30s: A Practical Guide</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>things to talk on a first date</t>
+          <t>dating in your 30s</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>KD 28, 1,000 vol.</t>
+          <t>KD 31, 720 vol. Life-stage cluster.</t>
         </is>
       </c>
     </row>
@@ -4308,23 +4308,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dating Tips for the First Date</t>
+          <t>How to Tell If a First Date Actually Went Well</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>dating tips first date</t>
+          <t>did the first date go well</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>KD 39, 1,000 vol.</t>
+          <t>Estimated — post-date advice cluster.</t>
         </is>
       </c>
     </row>
@@ -4357,23 +4357,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Best Date Night Questions for Couples</t>
+          <t>Senior Dating Services: A Thoughtful Alternative to Apps</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>date night questions</t>
+          <t>senior dating services</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>1300</v>
+        <v>2400</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>49</v>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>KD 24, 1,300 vol.</t>
+          <t>KD 49, 2,400 vol. Demographic service term.</t>
         </is>
       </c>
     </row>
@@ -4406,23 +4406,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Should You Kiss on the First Date? A Matchmaker Weighs In</t>
+          <t>Dating Over 50: How Matchmaking Beats the Apps</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>first date kiss</t>
+          <t>over 50 dating services</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>880</v>
+        <v>2900</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>46</v>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Estimated — common first-date AEO query.</t>
+          <t>KD 46, 2,900 vol.</t>
         </is>
       </c>
     </row>
@@ -4455,21 +4455,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Second Date Ideas That Build Momentum</t>
+          <t>How to Make a Great First Impression on a Date</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>second date ideas</t>
+          <t>first impression on a date</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>Estimated — natural follow-up to first-date cluster.</t>
+          <t>Estimated — coaching authority.</t>
         </is>
       </c>
     </row>
@@ -4504,21 +4504,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>How to Read Body Language on a Date</t>
+          <t>What Actually Makes Two People Compatible</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>body language on a date</t>
+          <t>compatibility factors relationship</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F81" s="8" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Estimated — coaching authority topic.</t>
+          <t>Estimated — ties coaching to your matching method.</t>
         </is>
       </c>
     </row>
@@ -4553,38 +4553,38 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Date Ideas in Boston, MA for Every Season</t>
+          <t>Do Matchmakers Actually Work? What the Results Show</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>date ideas boston ma</t>
+          <t>do matchmakers work</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>880</v>
+        <v>70</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>KD 21, 880 vol.</t>
+          <t>KD 23. Objection-handling content.</t>
         </is>
       </c>
     </row>
@@ -4602,38 +4602,38 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Date Ideas in Dallas, TX</t>
+          <t>What You're Really Paying For When You Hire a Matchmaker</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>date ideas dallas tx</t>
+          <t>professional matchmaker cost</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>880</v>
+        <v>70</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>KD 18, 880 vol.</t>
+          <t>KD 10. Value-framing of the investment.</t>
         </is>
       </c>
     </row>
@@ -4651,38 +4651,38 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Date Night in NYC: A Curated Evening</t>
+          <t>Why Singles Are Trading Dating Apps for Matchmakers</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>date night nyc</t>
+          <t>dating app vs matchmaker</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>880</v>
+        <v>300</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>KD 23, 880 vol.</t>
+          <t>Estimated — captures the app-fatigued buyer.</t>
         </is>
       </c>
     </row>
@@ -4700,28 +4700,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Date Night in Phoenix</t>
+          <t>What Separates a Great Matchmaker From the Rest</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>date night phoenix</t>
+          <t>what makes a good matchmaker</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>880</v>
+        <v>250</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>Local Dating Guides</t>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>KD 18, 880 vol.</t>
+          <t>Estimated — positions your standards.</t>
         </is>
       </c>
     </row>
@@ -4749,19 +4749,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Denver for Couples</t>
+          <t>Date Night in Washington, DC for Politicos and Romantics</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>date night ideas denver</t>
+          <t>date night ideas washington dc</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>880</v>
+        <v>210</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>KD 19, 880 vol.</t>
+          <t>KD 16, 210 vol.</t>
         </is>
       </c>
     </row>
@@ -4798,19 +4798,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Date Ideas in Los Angeles, CA</t>
+          <t>Date Night in Scottsdale, Done Right</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>date ideas in los angeles ca</t>
+          <t>date night scottsdale</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>KD 16, 1,000 vol.</t>
+          <t>KD 18, 210 vol.</t>
         </is>
       </c>
     </row>
@@ -4847,19 +4847,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Date Night in Dallas: A Local Guide</t>
+          <t>Where to Take a Date in Tucson</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>date night in dallas</t>
+          <t>date night tucson</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>720</v>
+        <v>170</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>KD 12, 720 vol.</t>
+          <t>KD 14, 170 vol.</t>
         </is>
       </c>
     </row>
@@ -4896,19 +4896,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Date Night Ideas in Dallas for Couples</t>
+          <t>Date Night in Reno Beyond the Casinos</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>dallas date night ideas</t>
+          <t>date night reno</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>KD 18, 1,000 vol.</t>
+          <t>KD 16, 140 vol.</t>
         </is>
       </c>
     </row>
@@ -4945,19 +4945,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Date Night in Atlanta, Georgia</t>
+          <t>Date Ideas in Birmingham for Southern Romance</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>date night atlanta georgia</t>
+          <t>date ideas birmingham</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>1300</v>
+        <v>90</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>KD 20, 1,300 vol.</t>
+          <t>KD 9, 90 vol.</t>
         </is>
       </c>
     </row>
@@ -4994,19 +4994,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Outdoor Date Ideas in Houston With Activities</t>
+          <t>First-Date Ideas in San Diego by the Coast</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>date ideas n houston with activity</t>
+          <t>first date ideas in san diego</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>KD 17, 1,000 vol.</t>
+          <t>KD 10, 70 vol.</t>
         </is>
       </c>
     </row>
@@ -5043,38 +5043,38 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Millionaire Matchmaker in Miami: High-End Introductions</t>
+          <t>Fun Date Ideas in Minneapolis, Rain, Snow, or Shine</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>millionaire matchmaker miami</t>
+          <t>fun date ideas in minneapolis</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G92" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>KD 13. Luxury-local page.</t>
+          <t>KD 6, 50 vol.</t>
         </is>
       </c>
     </row>
@@ -5092,38 +5092,38 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Matchmaker in Austin: What It Costs</t>
+          <t>Date Ideas in Naples, Florida for a Slower Pace</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>austin matchmakers cost</t>
+          <t>date ideas naples fl</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>KD 5. Local commercial-cost page.</t>
+          <t>KD 16, 40 vol.</t>
         </is>
       </c>
     </row>
@@ -5141,38 +5141,38 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jewish Matchmaker Near You</t>
+          <t>Date Ideas in Boise for Outdoorsy Couples</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>jewish matchmaker near me</t>
+          <t>date ideas boise id</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G94" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>KD 37. Faith-based niche page.</t>
+          <t>KD 24, 260 vol.</t>
         </is>
       </c>
     </row>
@@ -5190,38 +5190,38 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cleveland Matchmaker: Introductions in Cleveland</t>
+          <t>Date Night in Albuquerque Under the Desert Sky</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>cleveland matchmaker</t>
+          <t>date night albuquerque</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G95" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Estimated — new-metro money page.</t>
+          <t>KD 19, 260 vol.</t>
         </is>
       </c>
     </row>
@@ -5239,38 +5239,38 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Columbus Matchmaker</t>
+          <t>Date Night in Tulsa Worth Leaving the House For</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>columbus matchmaker</t>
+          <t>date night ideas tulsa</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G96" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>Estimated — new-metro money page.</t>
+          <t>KD 17, 590 vol.</t>
         </is>
       </c>
     </row>
@@ -5288,23 +5288,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Detroit Matchmaker: Meet Someone in Metro Detroit</t>
+          <t>Faith First: Finding a Christian Matchmaker Near You</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>detroit matchmaker</t>
+          <t>christian matchmaker near me</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>24</v>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Estimated — new-metro money page.</t>
+          <t>KD 24. Faith-based niche page.</t>
         </is>
       </c>
     </row>
@@ -5337,19 +5337,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Baltimore Matchmaker</t>
+          <t>Meet Your Match in Milwaukee</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>baltimore matchmaker</t>
+          <t>milwaukee matchmaker</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
         <v>400</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -5386,16 +5386,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Raleigh-Durham Matchmaker</t>
+          <t>A Personal Matchmaker for Louisville Singles</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>raleigh matchmaker</t>
+          <t>louisville matchmaker</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>14</v>
@@ -5435,19 +5435,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Reno Matchmaker: Introductions in Northern Nevada</t>
+          <t>Find Love in Buffalo Without the Apps</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>reno matchmaker</t>
+          <t>buffalo matchmaker</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>Estimated — Reno is a high-local-keyword metro in the set.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5484,19 +5484,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tucson Matchmaker</t>
+          <t>How Matchmaking Works in Hartford</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>tucson matchmaker</t>
+          <t>hartford matchmaker</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
@@ -5533,38 +5533,38 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>How Much Do Matchmakers Make? Inside the Profession</t>
+          <t>Introductions for Birmingham Singles</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>how much do matchmakers make</t>
+          <t>birmingham matchmaker</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>KD 14. Curiosity-driven, builds authority.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5582,38 +5582,38 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Matchmaking Services Cost: A Transparent Guide</t>
+          <t>Your Personal Matchmaker in Knoxville</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>matchmaking services cost</t>
+          <t>knoxville matchmaker</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>KD 6. Commercial cost query.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5631,38 +5631,38 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Do Matchmaking Services Really Work?</t>
+          <t>Boise Matchmaking, Handled for You</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>do matchmaking services work</t>
+          <t>boise matchmaker</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>10</v>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>KD 28. Objection-handling.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5680,38 +5680,38 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>How Background Checks Make Matchmaking Safer Than Apps</t>
+          <t>Meet Quality Singles in Des Moines</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>background check dating</t>
+          <t>des moines matchmaker</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>9</v>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>Estimated — your verification differentiator vs apps.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5729,38 +5729,38 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>What to Expect From Your First Matchmaking Consultation</t>
+          <t>A Personal Matchmaker for Naples Singles</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>matchmaking consultation</t>
+          <t>naples matchmaker</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>12</v>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>Estimated — moves prospects toward booking.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5778,38 +5778,38 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Matchmaker vs Dating App: The Real Difference in Outcomes</t>
+          <t>Find Love in Spokane Without the Apps</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>dating app vs matchmaker</t>
+          <t>spokane matchmaker</t>
         </is>
       </c>
       <c r="D107" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>9</v>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>Estimated — comparison cluster.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5827,38 +5827,38 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dating After Divorce: A Matchmaker's Roadmap</t>
+          <t>Meet Your Match in Albuquerque</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>dating after divorce</t>
+          <t>albuquerque matchmaker</t>
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G108" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>12</v>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>Estimated — high-empathy life-stage topic.</t>
+          <t>Estimated — new-metro money page.</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Dating in Your 40s: What's Different and What Works</t>
+          <t>Dating in Your 40s: What's Different, What Works</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -5890,7 +5890,7 @@
       <c r="E109" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dating in Your 50s and Beyond</t>
+          <t>Dating in Your 50s and Loving It</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -5939,7 +5939,7 @@
       <c r="E110" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5974,23 +5974,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals: How to Make Time</t>
+          <t>Dating After Divorce: A Matchmaker's Roadmap</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>dating for professionals</t>
+          <t>dating after divorce</t>
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>Estimated — speaks to your core client.</t>
+          <t>Estimated — high-empathy life-stage topic.</t>
         </is>
       </c>
     </row>
@@ -6023,23 +6023,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Over 50 Dating Services: How Matchmaking Fits</t>
+          <t>Dating Burnout: How to Reset After App Fatigue</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>over 50 dating services</t>
+          <t>dating burnout</t>
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>2900</v>
+        <v>600</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F112" s="13" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>27</v>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>KD 46, 2,900 vol. Demographic service term.</t>
+          <t>Estimated — captures the app-fatigued searcher.</t>
         </is>
       </c>
     </row>
@@ -6072,23 +6072,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Senior Dating Services: A Thoughtful Alternative to Apps</t>
+          <t>From Endless Swiping to a Real Relationship</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>senior dating services</t>
+          <t>online dating to relationship</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>2400</v>
+        <v>400</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="F113" s="13" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>32</v>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>KD 49, 2,400 vol.</t>
+          <t>Estimated — bridges app users to you.</t>
         </is>
       </c>
     </row>
@@ -6121,21 +6121,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Luxury Dating: What Discreet, High-End Matchmaking Looks Like</t>
+          <t>Dating for Busy Professionals: How to Make Time</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>luxury dating</t>
+          <t>dating for professionals</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>KD 28, 1,300 vol. On-brand positioning term.</t>
+          <t>Estimated — speaks to your core client.</t>
         </is>
       </c>
     </row>
@@ -6170,21 +6170,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Red Flags on a First Date (and Green Flags Too)</t>
+          <t>The Art of Texting After a First Date</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>first date red flags</t>
+          <t>texting after first date</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="F115" s="8" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Estimated — high-share advice topic.</t>
+          <t>Estimated — post-date cluster.</t>
         </is>
       </c>
     </row>
@@ -6219,23 +6219,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>How to Tell If a First Date Went Well</t>
+          <t>Why People Ghost, and How to Move On</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>did the first date go well</t>
+          <t>ghosting dating</t>
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Estimated — post-date advice cluster.</t>
+          <t>Estimated — high-share modern-dating topic.</t>
         </is>
       </c>
     </row>
@@ -6268,21 +6268,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>How to Move From Online Dating to a Real Relationship</t>
+          <t>Turning a Great Match Into a Lasting Relationship</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>online dating to relationship</t>
+          <t>lasting relationship advice</t>
         </is>
       </c>
       <c r="D117" s="4" t="n">
         <v>400</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F117" s="9" t="inlineStr">
+        <v>33</v>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Estimated — bridges app-fatigue audience to you.</t>
+          <t>Estimated — bridges matching to outcomes.</t>
         </is>
       </c>
     </row>
@@ -6317,21 +6317,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dating Burnout: How to Reset After App Fatigue</t>
+          <t>How to Start Dating Again After a Breakup</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>dating burnout</t>
+          <t>dating again after a breakup</t>
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>Estimated — captures the app-fatigued searcher.</t>
+          <t>Estimated — life-stage cluster.</t>
         </is>
       </c>
     </row>
@@ -6366,23 +6366,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>First Date Flowers: Sweet or Too Much?</t>
+          <t>First-Date Activities That Take the Pressure Off</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>first date flowers</t>
+          <t>first date activities</t>
         </is>
       </c>
       <c r="D119" s="4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>27</v>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>KD 6, 1,000 vol. Easy win.</t>
+          <t>Estimated — activity-led first-date angle.</t>
         </is>
       </c>
     </row>
@@ -6415,21 +6415,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>How to Make a Great First Impression on a Date</t>
+          <t>Chemistry vs Compatibility: Which Should You Trust?</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>first impression on a date</t>
+          <t>chemistry vs compatibility</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Estimated — coaching authority.</t>
+          <t>Estimated — ties to your matching philosophy.</t>
         </is>
       </c>
     </row>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>What Makes a Good Match? The Compatibility Factors That Matter</t>
+          <t>How to Flirt Without Trying Too Hard</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>compatibility factors relationship</t>
+          <t>how to flirt</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>Estimated — ties coaching to your matching method.</t>
+          <t>Estimated — broad coaching authority topic.</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G478"/>
+  <dimension ref="A1:G497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6579,7 +6579,7 @@
       <c r="C2" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6612,7 +6612,7 @@
       <c r="C3" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6744,7 +6744,7 @@
       <c r="C7" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6777,7 +6777,7 @@
       <c r="C8" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6810,7 +6810,7 @@
       <c r="C9" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6876,7 +6876,7 @@
       <c r="C11" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6975,7 +6975,7 @@
       <c r="C14" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7008,7 +7008,7 @@
       <c r="C15" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7041,7 +7041,7 @@
       <c r="C16" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7074,7 +7074,7 @@
       <c r="C17" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7122,9 +7122,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       <c r="C19" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7173,7 +7173,7 @@
       <c r="C20" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7305,7 +7305,7 @@
       <c r="C24" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7320,9 +7320,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       <c r="C25" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7371,7 +7371,7 @@
       <c r="C26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7386,9 +7386,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       <c r="C30" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7536,7 +7536,7 @@
       <c r="C31" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7635,7 +7635,7 @@
       <c r="C34" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7650,9 +7650,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       <c r="C35" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7734,7 +7734,7 @@
       <c r="C37" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7749,9 +7749,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
       <c r="C38" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7815,9 +7815,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       <c r="C40" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7932,7 +7932,7 @@
       <c r="C43" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7965,7 +7965,7 @@
       <c r="C44" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7998,7 +7998,7 @@
       <c r="C45" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8013,9 +8013,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       <c r="C46" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8046,9 +8046,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       <c r="C47" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8097,7 +8097,7 @@
       <c r="C48" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8112,9 +8112,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       <c r="C49" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8145,9 +8145,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="C50" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8196,7 +8196,7 @@
       <c r="C51" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8262,7 +8262,7 @@
       <c r="C53" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8295,7 +8295,7 @@
       <c r="C54" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8361,7 +8361,7 @@
       <c r="C56" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8376,9 +8376,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G56" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8442,9 +8442,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G58" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8475,9 +8475,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G59" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       <c r="C60" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8526,7 +8526,7 @@
       <c r="C61" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8625,7 +8625,7 @@
       <c r="C64" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8658,7 +8658,7 @@
       <c r="C65" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8691,7 +8691,7 @@
       <c r="C66" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8724,7 +8724,7 @@
       <c r="C67" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8739,9 +8739,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G67" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       <c r="C68" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8772,9 +8772,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G68" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       <c r="C69" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8805,9 +8805,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G69" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       <c r="C70" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8856,7 +8856,7 @@
       <c r="C71" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8889,7 +8889,7 @@
       <c r="C72" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8988,7 +8988,7 @@
       <c r="C75" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9021,7 +9021,7 @@
       <c r="C76" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9054,7 +9054,7 @@
       <c r="C77" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9087,7 +9087,7 @@
       <c r="C78" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9135,9 +9135,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G79" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9168,9 +9168,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G80" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9201,9 +9201,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G81" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       <c r="C83" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9267,9 +9267,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G83" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9333,9 +9333,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G85" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       <c r="C86" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9366,9 +9366,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G86" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       <c r="C88" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9432,9 +9432,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G88" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       <c r="C89" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D89" s="9" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9465,9 +9465,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G89" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       <c r="C90" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9582,7 +9582,7 @@
       <c r="C93" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9597,9 +9597,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G93" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
       <c r="C94" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D94" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9630,9 +9630,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G94" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9663,9 +9663,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G95" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       <c r="C98" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D98" s="9" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9828,9 +9828,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G100" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       <c r="C101" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D101" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9861,9 +9861,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G101" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9894,9 +9894,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G102" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       <c r="C106" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10044,7 +10044,7 @@
       <c r="C107" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D107" s="9" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10077,7 +10077,7 @@
       <c r="C108" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10110,7 +10110,7 @@
       <c r="C109" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10275,7 +10275,7 @@
       <c r="C114" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D114" s="8" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10308,7 +10308,7 @@
       <c r="C115" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D115" s="9" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10341,7 +10341,7 @@
       <c r="C116" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D116" s="8" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10440,7 +10440,7 @@
       <c r="C119" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D119" s="8" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10473,7 +10473,7 @@
       <c r="C120" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D120" s="9" t="inlineStr">
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10521,9 +10521,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G121" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10605,7 @@
       <c r="C124" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D124" s="8" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10653,9 +10653,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G125" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10719,9 +10719,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G127" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       <c r="C129" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D129" s="8" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10851,9 +10851,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G131" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10983,9 +10983,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G135" s="15" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       <c r="C137" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D137" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11067,7 +11067,7 @@
       <c r="C138" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D138" s="9" t="inlineStr">
+      <c r="D138" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11133,7 +11133,7 @@
       <c r="C140" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D140" s="8" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11166,7 +11166,7 @@
       <c r="C141" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D141" s="8" t="inlineStr">
+      <c r="D141" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11199,7 +11199,7 @@
       <c r="C142" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D142" s="8" t="inlineStr">
+      <c r="D142" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11430,7 +11430,7 @@
       <c r="C149" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D149" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11463,7 +11463,7 @@
       <c r="C150" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D150" s="9" t="inlineStr">
+      <c r="D150" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11496,7 +11496,7 @@
       <c r="C151" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D151" s="8" t="inlineStr">
+      <c r="D151" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11529,7 +11529,7 @@
       <c r="C152" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="D152" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11562,7 +11562,7 @@
       <c r="C153" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D153" s="8" t="inlineStr">
+      <c r="D153" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11694,7 +11694,7 @@
       <c r="C157" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D157" s="8" t="inlineStr">
+      <c r="D157" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11742,9 +11742,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G158" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G158" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       <c r="C159" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D159" s="8" t="inlineStr">
+      <c r="D159" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11973,9 +11973,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G165" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G165" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       <c r="C168" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D168" s="8" t="inlineStr">
+      <c r="D168" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12072,9 +12072,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G168" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G168" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       <c r="C171" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D171" s="8" t="inlineStr">
+      <c r="D171" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12222,7 +12222,7 @@
       <c r="C173" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D173" s="8" t="inlineStr">
+      <c r="D173" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12336,9 +12336,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G176" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G176" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       <c r="C178" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D178" s="8" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12420,7 +12420,7 @@
       <c r="C179" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D179" s="8" t="inlineStr">
+      <c r="D179" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12519,7 +12519,7 @@
       <c r="C182" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D182" s="8" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12552,7 +12552,7 @@
       <c r="C183" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D183" s="8" t="inlineStr">
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12585,7 +12585,7 @@
       <c r="C184" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D184" s="9" t="inlineStr">
+      <c r="D184" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12651,7 +12651,7 @@
       <c r="C186" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D186" s="8" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12717,7 +12717,7 @@
       <c r="C188" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D188" s="8" t="inlineStr">
+      <c r="D188" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12750,7 +12750,7 @@
       <c r="C189" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D189" s="8" t="inlineStr">
+      <c r="D189" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12783,7 +12783,7 @@
       <c r="C190" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D190" s="9" t="inlineStr">
+      <c r="D190" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12882,7 +12882,7 @@
       <c r="C193" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D193" s="8" t="inlineStr">
+      <c r="D193" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12948,7 +12948,7 @@
       <c r="C195" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D195" s="8" t="inlineStr">
+      <c r="D195" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12981,7 +12981,7 @@
       <c r="C196" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D196" s="8" t="inlineStr">
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13047,7 +13047,7 @@
       <c r="C198" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D198" s="9" t="inlineStr">
+      <c r="D198" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13080,7 +13080,7 @@
       <c r="C199" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D199" s="8" t="inlineStr">
+      <c r="D199" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13113,7 +13113,7 @@
       <c r="C200" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D200" s="9" t="inlineStr">
+      <c r="D200" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13146,7 +13146,7 @@
       <c r="C201" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D201" s="8" t="inlineStr">
+      <c r="D201" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13245,7 +13245,7 @@
       <c r="C204" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D204" s="8" t="inlineStr">
+      <c r="D204" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13326,9 +13326,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G206" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G206" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13359,9 +13359,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G207" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G207" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13656,9 +13656,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G216" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G216" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13674,7 +13674,7 @@
       <c r="C217" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D217" s="8" t="inlineStr">
+      <c r="D217" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13722,9 +13722,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G218" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G218" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13872,7 @@
       <c r="C223" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D223" s="9" t="inlineStr">
+      <c r="D223" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13971,7 +13971,7 @@
       <c r="C226" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D226" s="8" t="inlineStr">
+      <c r="D226" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14004,7 +14004,7 @@
       <c r="C227" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D227" s="8" t="inlineStr">
+      <c r="D227" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14136,7 +14136,7 @@
       <c r="C231" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D231" s="8" t="inlineStr">
+      <c r="D231" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14268,7 +14268,7 @@
       <c r="C235" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D235" s="9" t="inlineStr">
+      <c r="D235" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14367,7 +14367,7 @@
       <c r="C238" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D238" s="9" t="inlineStr">
+      <c r="D238" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14400,7 +14400,7 @@
       <c r="C239" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D239" s="8" t="inlineStr">
+      <c r="D239" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14433,7 +14433,7 @@
       <c r="C240" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D240" s="8" t="inlineStr">
+      <c r="D240" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14499,7 +14499,7 @@
       <c r="C242" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D242" s="8" t="inlineStr">
+      <c r="D242" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14532,7 +14532,7 @@
       <c r="C243" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D243" s="8" t="inlineStr">
+      <c r="D243" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14565,7 +14565,7 @@
       <c r="C244" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D244" s="9" t="inlineStr">
+      <c r="D244" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14631,7 +14631,7 @@
       <c r="C246" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D246" s="8" t="inlineStr">
+      <c r="D246" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14730,7 +14730,7 @@
       <c r="C249" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D249" s="9" t="inlineStr">
+      <c r="D249" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14763,7 +14763,7 @@
       <c r="C250" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="D250" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14796,7 +14796,7 @@
       <c r="C251" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D251" s="9" t="inlineStr">
+      <c r="D251" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14862,7 +14862,7 @@
       <c r="C253" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D253" s="8" t="inlineStr">
+      <c r="D253" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14928,7 +14928,7 @@
       <c r="C255" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D255" s="8" t="inlineStr">
+      <c r="D255" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15027,7 +15027,7 @@
       <c r="C258" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D258" s="9" t="inlineStr">
+      <c r="D258" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15225,7 +15225,7 @@
       <c r="C264" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D264" s="8" t="inlineStr">
+      <c r="D264" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15291,7 +15291,7 @@
       <c r="C266" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D266" s="8" t="inlineStr">
+      <c r="D266" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15306,9 +15306,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G266" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G266" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -15324,7 +15324,7 @@
       <c r="C267" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D267" s="8" t="inlineStr">
+      <c r="D267" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15489,7 +15489,7 @@
       <c r="C272" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D272" s="8" t="inlineStr">
+      <c r="D272" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15522,7 +15522,7 @@
       <c r="C273" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D273" s="8" t="inlineStr">
+      <c r="D273" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15555,7 +15555,7 @@
       <c r="C274" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D274" s="8" t="inlineStr">
+      <c r="D274" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15588,7 +15588,7 @@
       <c r="C275" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D275" s="8" t="inlineStr">
+      <c r="D275" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15687,7 +15687,7 @@
       <c r="C278" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D278" s="8" t="inlineStr">
+      <c r="D278" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15819,7 +15819,7 @@
       <c r="C282" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D282" s="8" t="inlineStr">
+      <c r="D282" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15867,9 +15867,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G283" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G283" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15918,7 @@
       <c r="C285" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D285" s="8" t="inlineStr">
+      <c r="D285" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16017,7 +16017,7 @@
       <c r="C288" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D288" s="9" t="inlineStr">
+      <c r="D288" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16149,7 +16149,7 @@
       <c r="C292" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D292" s="9" t="inlineStr">
+      <c r="D292" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16182,7 +16182,7 @@
       <c r="C293" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D293" s="8" t="inlineStr">
+      <c r="D293" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16281,7 +16281,7 @@
       <c r="C296" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D296" s="9" t="inlineStr">
+      <c r="D296" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16347,7 +16347,7 @@
       <c r="C298" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D298" s="8" t="inlineStr">
+      <c r="D298" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16479,7 +16479,7 @@
       <c r="C302" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D302" s="9" t="inlineStr">
+      <c r="D302" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16512,7 +16512,7 @@
       <c r="C303" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D303" s="9" t="inlineStr">
+      <c r="D303" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16578,7 +16578,7 @@
       <c r="C305" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D305" s="9" t="inlineStr">
+      <c r="D305" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16776,7 +16776,7 @@
       <c r="C311" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D311" s="8" t="inlineStr">
+      <c r="D311" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17007,7 +17007,7 @@
       <c r="C318" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D318" s="8" t="inlineStr">
+      <c r="D318" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17073,7 +17073,7 @@
       <c r="C320" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D320" s="8" t="inlineStr">
+      <c r="D320" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17139,7 +17139,7 @@
       <c r="C322" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D322" s="8" t="inlineStr">
+      <c r="D322" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17205,7 +17205,7 @@
       <c r="C324" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D324" s="8" t="inlineStr">
+      <c r="D324" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17271,7 +17271,7 @@
       <c r="C326" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D326" s="8" t="inlineStr">
+      <c r="D326" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17370,7 +17370,7 @@
       <c r="C329" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D329" s="8" t="inlineStr">
+      <c r="D329" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17403,7 +17403,7 @@
       <c r="C330" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D330" s="8" t="inlineStr">
+      <c r="D330" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17436,7 +17436,7 @@
       <c r="C331" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D331" s="8" t="inlineStr">
+      <c r="D331" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17832,7 +17832,7 @@
       <c r="C343" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D343" s="8" t="inlineStr">
+      <c r="D343" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17865,7 +17865,7 @@
       <c r="C344" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D344" s="8" t="inlineStr">
+      <c r="D344" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18129,7 +18129,7 @@
       <c r="C352" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D352" s="8" t="inlineStr">
+      <c r="D352" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18261,7 +18261,7 @@
       <c r="C356" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D356" s="8" t="inlineStr">
+      <c r="D356" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18360,7 +18360,7 @@
       <c r="C359" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D359" s="8" t="inlineStr">
+      <c r="D359" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18393,7 +18393,7 @@
       <c r="C360" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D360" s="8" t="inlineStr">
+      <c r="D360" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18426,7 +18426,7 @@
       <c r="C361" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D361" s="8" t="inlineStr">
+      <c r="D361" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18459,7 +18459,7 @@
       <c r="C362" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D362" s="8" t="inlineStr">
+      <c r="D362" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18525,7 +18525,7 @@
       <c r="C364" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D364" s="8" t="inlineStr">
+      <c r="D364" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18558,7 +18558,7 @@
       <c r="C365" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D365" s="9" t="inlineStr">
+      <c r="D365" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18591,7 +18591,7 @@
       <c r="C366" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D366" s="8" t="inlineStr">
+      <c r="D366" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18657,7 +18657,7 @@
       <c r="C368" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D368" s="9" t="inlineStr">
+      <c r="D368" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18690,7 +18690,7 @@
       <c r="C369" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D369" s="9" t="inlineStr">
+      <c r="D369" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18723,7 +18723,7 @@
       <c r="C370" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D370" s="8" t="inlineStr">
+      <c r="D370" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18756,7 +18756,7 @@
       <c r="C371" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D371" s="8" t="inlineStr">
+      <c r="D371" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18822,7 +18822,7 @@
       <c r="C373" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D373" s="8" t="inlineStr">
+      <c r="D373" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18855,7 +18855,7 @@
       <c r="C374" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D374" s="9" t="inlineStr">
+      <c r="D374" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18888,7 +18888,7 @@
       <c r="C375" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D375" s="8" t="inlineStr">
+      <c r="D375" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -19053,7 +19053,7 @@
       <c r="C380" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D380" s="8" t="inlineStr">
+      <c r="D380" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -19086,7 +19086,7 @@
       <c r="C381" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D381" s="8" t="inlineStr">
+      <c r="D381" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -19185,7 +19185,7 @@
       <c r="C384" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D384" s="8" t="inlineStr">
+      <c r="D384" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -19284,7 +19284,7 @@
       <c r="C387" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D387" s="9" t="inlineStr">
+      <c r="D387" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19317,7 +19317,7 @@
       <c r="C388" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D388" s="9" t="inlineStr">
+      <c r="D388" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19416,7 +19416,7 @@
       <c r="C391" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D391" s="9" t="inlineStr">
+      <c r="D391" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19449,7 +19449,7 @@
       <c r="C392" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D392" s="9" t="inlineStr">
+      <c r="D392" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19746,7 +19746,7 @@
       <c r="C401" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D401" s="9" t="inlineStr">
+      <c r="D401" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19779,7 +19779,7 @@
       <c r="C402" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D402" s="9" t="inlineStr">
+      <c r="D402" s="8" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19845,7 +19845,7 @@
       <c r="C404" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D404" s="8" t="inlineStr">
+      <c r="D404" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -19878,7 +19878,7 @@
       <c r="C405" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D405" s="8" t="inlineStr">
+      <c r="D405" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -19893,9 +19893,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G405" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G405" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       <c r="C410" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D410" s="8" t="inlineStr">
+      <c r="D410" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -20289,9 +20289,9 @@
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="G417" s="14" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G417" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -20373,7 +20373,7 @@
       <c r="C420" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D420" s="8" t="inlineStr">
+      <c r="D420" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -20463,18 +20463,18 @@
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
         <is>
-          <t>do matchmakers work</t>
+          <t>what is matchmaking</t>
         </is>
       </c>
       <c r="B423" s="4" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="C423" s="2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E423" s="6" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G423" s="15" t="inlineStr">
@@ -20496,18 +20496,18 @@
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
         <is>
-          <t>what is matchmaking</t>
+          <t>hire a matchmaker</t>
         </is>
       </c>
       <c r="B424" s="4" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="C424" s="2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D424" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E424" s="6" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="G424" s="15" t="inlineStr">
@@ -20529,16 +20529,16 @@
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
         <is>
-          <t>hire a matchmaker</t>
+          <t>matchmaker vs online dating</t>
         </is>
       </c>
       <c r="B425" s="4" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="C425" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="D425" s="8" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="D425" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -20562,18 +20562,18 @@
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
         <is>
-          <t>professional matchmaker cost</t>
+          <t>are matchmakers still a thing</t>
         </is>
       </c>
       <c r="B426" s="4" t="n">
         <v>70</v>
       </c>
       <c r="C426" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D426" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>31</v>
+      </c>
+      <c r="D426" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E426" s="6" t="inlineStr">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G426" s="15" t="inlineStr">
@@ -20595,28 +20595,28 @@
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
         <is>
-          <t>matchmaker vs online dating</t>
+          <t>matchmaker near me</t>
         </is>
       </c>
       <c r="B427" s="4" t="n">
-        <v>320</v>
+        <v>2400</v>
       </c>
       <c r="C427" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D427" s="8" t="inlineStr">
+        <v>24</v>
+      </c>
+      <c r="D427" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E427" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+      <c r="E427" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G427" s="15" t="inlineStr">
@@ -20628,28 +20628,28 @@
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
         <is>
-          <t>are matchmakers still a thing</t>
+          <t>san francisco matchmaker</t>
         </is>
       </c>
       <c r="B428" s="4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C428" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D428" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E428" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>6</v>
+      </c>
+      <c r="D428" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E428" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G428" s="15" t="inlineStr">
@@ -20694,14 +20694,14 @@
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
         <is>
-          <t>san francisco matchmaker</t>
+          <t>new jersey matchmaker</t>
         </is>
       </c>
       <c r="B430" s="4" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C430" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
@@ -20727,14 +20727,14 @@
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
         <is>
-          <t>new jersey matchmaker</t>
+          <t>gay matchmaker los angeles</t>
         </is>
       </c>
       <c r="B431" s="4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C431" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
@@ -20760,18 +20760,18 @@
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
         <is>
-          <t>pittsburgh matchmaker</t>
+          <t>matchmaker tucson</t>
         </is>
       </c>
       <c r="B432" s="4" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="C432" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D432" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>5</v>
+      </c>
+      <c r="D432" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E432" s="11" t="inlineStr">
@@ -20793,18 +20793,18 @@
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
         <is>
-          <t>professional matchmaker nyc</t>
+          <t>matchmaker memphis</t>
         </is>
       </c>
       <c r="B433" s="4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C433" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D433" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>2</v>
+      </c>
+      <c r="D433" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E433" s="11" t="inlineStr">
@@ -20826,18 +20826,18 @@
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
         <is>
-          <t>matchmaker charlotte nc</t>
+          <t>reno matchmaker</t>
         </is>
       </c>
       <c r="B434" s="4" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="C434" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D434" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>8</v>
+      </c>
+      <c r="D434" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E434" s="11" t="inlineStr">
@@ -20859,14 +20859,14 @@
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
         <is>
-          <t>elite matchmaking nyc</t>
+          <t>tulsa matchmaker</t>
         </is>
       </c>
       <c r="B435" s="4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C435" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
@@ -20892,18 +20892,18 @@
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
         <is>
-          <t>matchmaker near me</t>
+          <t>omaha matchmaker</t>
         </is>
       </c>
       <c r="B436" s="4" t="n">
-        <v>2400</v>
+        <v>30</v>
       </c>
       <c r="C436" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D436" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>20</v>
+      </c>
+      <c r="D436" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E436" s="11" t="inlineStr">
@@ -20934,7 +20934,7 @@
       <c r="C437" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D437" s="8" t="inlineStr">
+      <c r="D437" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -20967,7 +20967,7 @@
       <c r="C438" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D438" s="8" t="inlineStr">
+      <c r="D438" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -20991,28 +20991,28 @@
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
         <is>
-          <t>jewish matchmaker nyc</t>
+          <t>first date red flags</t>
         </is>
       </c>
       <c r="B439" s="4" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="C439" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D439" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E439" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>28</v>
+      </c>
+      <c r="D439" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E439" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G439" s="15" t="inlineStr">
@@ -21024,28 +21024,28 @@
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
         <is>
-          <t>gay matchmaker los angeles</t>
+          <t>how much do matchmakers make</t>
         </is>
       </c>
       <c r="B440" s="4" t="n">
         <v>110</v>
       </c>
       <c r="C440" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E440" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+      <c r="E440" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G440" s="15" t="inlineStr">
@@ -21057,28 +21057,28 @@
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
         <is>
-          <t>gay matchmaker nyc</t>
+          <t>matchmaking consultation</t>
         </is>
       </c>
       <c r="B441" s="4" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="C441" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D441" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E441" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>22</v>
+      </c>
+      <c r="D441" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E441" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="G441" s="15" t="inlineStr">
@@ -21090,28 +21090,28 @@
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
         <is>
-          <t>elite matchmaker new york</t>
+          <t>background check dating</t>
         </is>
       </c>
       <c r="B442" s="4" t="n">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="C442" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D442" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E442" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>30</v>
+      </c>
+      <c r="D442" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E442" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="G442" s="15" t="inlineStr">
@@ -21123,28 +21123,28 @@
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
         <is>
-          <t>christian matchmaker near me</t>
+          <t>matchmaking services cost</t>
         </is>
       </c>
       <c r="B443" s="4" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="C443" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D443" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E443" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>6</v>
+      </c>
+      <c r="D443" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E443" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="G443" s="15" t="inlineStr">
@@ -21156,18 +21156,18 @@
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
         <is>
-          <t>matchmaker pittsburgh pa</t>
+          <t>pittsburgh matchmaker</t>
         </is>
       </c>
       <c r="B444" s="4" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C444" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D444" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>29</v>
+      </c>
+      <c r="D444" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E444" s="11" t="inlineStr">
@@ -21189,18 +21189,18 @@
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
         <is>
-          <t>matchmaker nyc cost</t>
+          <t>matchmaker charlotte nc</t>
         </is>
       </c>
       <c r="B445" s="4" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="C445" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D445" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>27</v>
+      </c>
+      <c r="D445" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E445" s="11" t="inlineStr">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G445" s="15" t="inlineStr">
@@ -21222,14 +21222,14 @@
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
         <is>
-          <t>tulsa matchmaker</t>
+          <t>jewish matchmaker nyc</t>
         </is>
       </c>
       <c r="B446" s="4" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="C446" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
@@ -21255,14 +21255,14 @@
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
         <is>
-          <t>omaha matchmaker</t>
+          <t>millionaire matchmaker miami</t>
         </is>
       </c>
       <c r="B447" s="4" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="C447" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
@@ -21321,14 +21321,14 @@
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
         <is>
-          <t>cincinnati matchmaker</t>
+          <t>cleveland matchmaker</t>
         </is>
       </c>
       <c r="B449" s="4" t="n">
         <v>500</v>
       </c>
       <c r="C449" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
@@ -21354,28 +21354,28 @@
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
         <is>
-          <t>first date kiss</t>
+          <t>columbus matchmaker</t>
         </is>
       </c>
       <c r="B450" s="4" t="n">
-        <v>880</v>
+        <v>500</v>
       </c>
       <c r="C450" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D450" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E450" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>15</v>
+      </c>
+      <c r="D450" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E450" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G450" s="15" t="inlineStr">
@@ -21387,28 +21387,28 @@
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
         <is>
-          <t>second date ideas</t>
+          <t>detroit matchmaker</t>
         </is>
       </c>
       <c r="B451" s="4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="C451" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D451" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E451" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>17</v>
+      </c>
+      <c r="D451" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E451" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G451" s="15" t="inlineStr">
@@ -21420,28 +21420,28 @@
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
         <is>
-          <t>body language on a date</t>
+          <t>baltimore matchmaker</t>
         </is>
       </c>
       <c r="B452" s="4" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="C452" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D452" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E452" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>16</v>
+      </c>
+      <c r="D452" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E452" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G452" s="15" t="inlineStr">
@@ -21453,14 +21453,14 @@
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
         <is>
-          <t>millionaire matchmaker miami</t>
+          <t>raleigh matchmaker</t>
         </is>
       </c>
       <c r="B453" s="4" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="C453" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
@@ -21486,14 +21486,14 @@
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
         <is>
-          <t>austin matchmakers cost</t>
+          <t>cincinnati matchmaker</t>
         </is>
       </c>
       <c r="B454" s="4" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="C454" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G454" s="15" t="inlineStr">
@@ -21519,28 +21519,28 @@
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
         <is>
-          <t>jewish matchmaker near me</t>
+          <t>second date ideas</t>
         </is>
       </c>
       <c r="B455" s="4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="C455" s="2" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D455" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E455" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E455" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G455" s="15" t="inlineStr">
@@ -21552,28 +21552,28 @@
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
         <is>
-          <t>cleveland matchmaker</t>
+          <t>body language on a date</t>
         </is>
       </c>
       <c r="B456" s="4" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="C456" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D456" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E456" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>28</v>
+      </c>
+      <c r="D456" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E456" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G456" s="15" t="inlineStr">
@@ -21585,28 +21585,28 @@
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
         <is>
-          <t>columbus matchmaker</t>
+          <t>first date kiss</t>
         </is>
       </c>
       <c r="B457" s="4" t="n">
-        <v>500</v>
+        <v>880</v>
       </c>
       <c r="C457" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D457" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E457" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>26</v>
+      </c>
+      <c r="D457" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E457" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G457" s="15" t="inlineStr">
@@ -21618,28 +21618,28 @@
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
         <is>
-          <t>detroit matchmaker</t>
+          <t>did the first date go well</t>
         </is>
       </c>
       <c r="B458" s="4" t="n">
         <v>500</v>
       </c>
       <c r="C458" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D458" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E458" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>26</v>
+      </c>
+      <c r="D458" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E458" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G458" s="15" t="inlineStr">
@@ -21651,28 +21651,28 @@
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
         <is>
-          <t>baltimore matchmaker</t>
+          <t>first impression on a date</t>
         </is>
       </c>
       <c r="B459" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C459" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D459" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E459" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>29</v>
+      </c>
+      <c r="D459" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E459" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G459" s="15" t="inlineStr">
@@ -21684,28 +21684,28 @@
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
         <is>
-          <t>raleigh matchmaker</t>
+          <t>compatibility factors relationship</t>
         </is>
       </c>
       <c r="B460" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C460" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D460" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E460" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>30</v>
+      </c>
+      <c r="D460" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E460" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G460" s="15" t="inlineStr">
@@ -21717,28 +21717,28 @@
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
         <is>
-          <t>reno matchmaker</t>
+          <t>do matchmakers work</t>
         </is>
       </c>
       <c r="B461" s="4" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="C461" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D461" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E461" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>23</v>
+      </c>
+      <c r="D461" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E461" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="G461" s="15" t="inlineStr">
@@ -21750,28 +21750,28 @@
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
         <is>
-          <t>tucson matchmaker</t>
+          <t>professional matchmaker cost</t>
         </is>
       </c>
       <c r="B462" s="4" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="C462" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
       </c>
-      <c r="E462" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+      <c r="E462" s="6" t="inlineStr">
+        <is>
+          <t>Matchmaking 101 &amp; Cost</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="G462" s="15" t="inlineStr">
@@ -21783,18 +21783,18 @@
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
         <is>
-          <t>how much do matchmakers make</t>
+          <t>dating app vs matchmaker</t>
         </is>
       </c>
       <c r="B463" s="4" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="C463" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D463" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>30</v>
+      </c>
+      <c r="D463" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E463" s="6" t="inlineStr">
@@ -21804,7 +21804,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Middle of funnel</t>
         </is>
       </c>
       <c r="G463" s="15" t="inlineStr">
@@ -21816,14 +21816,14 @@
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
         <is>
-          <t>matchmaking services cost</t>
+          <t>what makes a good matchmaker</t>
         </is>
       </c>
       <c r="B464" s="4" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="C464" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G464" s="15" t="inlineStr">
@@ -21849,28 +21849,28 @@
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
         <is>
-          <t>do matchmaking services work</t>
+          <t>date night ideas washington dc</t>
         </is>
       </c>
       <c r="B465" s="4" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="C465" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D465" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E465" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>16</v>
+      </c>
+      <c r="D465" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E465" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G465" s="15" t="inlineStr">
@@ -21882,28 +21882,28 @@
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
         <is>
-          <t>background check dating</t>
+          <t>date night scottsdale</t>
         </is>
       </c>
       <c r="B466" s="4" t="n">
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="C466" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D466" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E466" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>18</v>
+      </c>
+      <c r="D466" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E466" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G466" s="15" t="inlineStr">
@@ -21915,28 +21915,28 @@
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
         <is>
-          <t>matchmaking consultation</t>
+          <t>date night tucson</t>
         </is>
       </c>
       <c r="B467" s="4" t="n">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="C467" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D467" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E467" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>14</v>
+      </c>
+      <c r="D467" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E467" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G467" s="15" t="inlineStr">
@@ -21948,28 +21948,28 @@
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
         <is>
-          <t>dating app vs matchmaker</t>
+          <t>date night reno</t>
         </is>
       </c>
       <c r="B468" s="4" t="n">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="C468" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D468" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E468" s="6" t="inlineStr">
-        <is>
-          <t>Matchmaking 101 &amp; Cost</t>
+        <v>16</v>
+      </c>
+      <c r="D468" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E468" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G468" s="15" t="inlineStr">
@@ -21981,23 +21981,23 @@
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
         <is>
-          <t>dating after divorce</t>
+          <t>date ideas birmingham</t>
         </is>
       </c>
       <c r="B469" s="4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="C469" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D469" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E469" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>9</v>
+      </c>
+      <c r="D469" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E469" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -22014,23 +22014,23 @@
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
         <is>
-          <t>dating in your 40s</t>
+          <t>first date ideas in san diego</t>
         </is>
       </c>
       <c r="B470" s="4" t="n">
-        <v>720</v>
+        <v>70</v>
       </c>
       <c r="C470" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D470" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E470" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>10</v>
+      </c>
+      <c r="D470" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E470" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -22047,23 +22047,23 @@
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
         <is>
-          <t>dating in your 50s</t>
+          <t>fun date ideas in minneapolis</t>
         </is>
       </c>
       <c r="B471" s="4" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C471" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D471" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E471" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>6</v>
+      </c>
+      <c r="D471" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E471" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -22080,28 +22080,28 @@
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
         <is>
-          <t>dating for professionals</t>
+          <t>date ideas naples fl</t>
         </is>
       </c>
       <c r="B472" s="4" t="n">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="C472" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D472" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E472" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>16</v>
+      </c>
+      <c r="D472" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E472" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G472" s="15" t="inlineStr">
@@ -22113,28 +22113,28 @@
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
         <is>
-          <t>first date red flags</t>
+          <t>christian matchmaker near me</t>
         </is>
       </c>
       <c r="B473" s="4" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="C473" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D473" s="8" t="inlineStr">
+        <v>24</v>
+      </c>
+      <c r="D473" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E473" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+      <c r="E473" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G473" s="15" t="inlineStr">
@@ -22146,28 +22146,28 @@
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
         <is>
-          <t>did the first date go well</t>
+          <t>milwaukee matchmaker</t>
         </is>
       </c>
       <c r="B474" s="4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C474" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D474" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E474" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>15</v>
+      </c>
+      <c r="D474" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E474" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G474" s="15" t="inlineStr">
@@ -22179,28 +22179,28 @@
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
         <is>
-          <t>online dating to relationship</t>
+          <t>louisville matchmaker</t>
         </is>
       </c>
       <c r="B475" s="4" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C475" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D475" s="9" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E475" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>14</v>
+      </c>
+      <c r="D475" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E475" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Middle of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G475" s="15" t="inlineStr">
@@ -22212,28 +22212,28 @@
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
         <is>
-          <t>dating burnout</t>
+          <t>buffalo matchmaker</t>
         </is>
       </c>
       <c r="B476" s="4" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C476" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D476" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E476" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>13</v>
+      </c>
+      <c r="D476" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E476" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G476" s="15" t="inlineStr">
@@ -22245,28 +22245,28 @@
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
         <is>
-          <t>first impression on a date</t>
+          <t>hartford matchmaker</t>
         </is>
       </c>
       <c r="B477" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C477" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D477" s="8" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E477" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
+        <v>14</v>
+      </c>
+      <c r="D477" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E477" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>Top of funnel</t>
+          <t>Bottom of funnel</t>
         </is>
       </c>
       <c r="G477" s="15" t="inlineStr">
@@ -22278,31 +22278,658 @@
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
         <is>
-          <t>compatibility factors relationship</t>
+          <t>birmingham matchmaker</t>
         </is>
       </c>
       <c r="B478" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="C478" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D478" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E478" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="G478" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="3" t="inlineStr">
+        <is>
+          <t>knoxville matchmaker</t>
+        </is>
+      </c>
+      <c r="B479" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="C479" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D479" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E479" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="G479" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="3" t="inlineStr">
+        <is>
+          <t>boise matchmaker</t>
+        </is>
+      </c>
+      <c r="B480" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="C480" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D480" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E480" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="G480" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="3" t="inlineStr">
+        <is>
+          <t>des moines matchmaker</t>
+        </is>
+      </c>
+      <c r="B481" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="C481" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D481" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E481" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="G481" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="3" t="inlineStr">
+        <is>
+          <t>naples matchmaker</t>
+        </is>
+      </c>
+      <c r="B482" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="C482" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D482" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E482" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="G482" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="3" t="inlineStr">
+        <is>
+          <t>spokane matchmaker</t>
+        </is>
+      </c>
+      <c r="B483" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="C483" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D483" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E483" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="G483" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="3" t="inlineStr">
+        <is>
+          <t>albuquerque matchmaker</t>
+        </is>
+      </c>
+      <c r="B484" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="C484" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D484" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E484" s="11" t="inlineStr">
+        <is>
+          <t>City Matchmaker Pages</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="G484" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="3" t="inlineStr">
+        <is>
+          <t>dating in your 40s</t>
+        </is>
+      </c>
+      <c r="B485" s="4" t="n">
+        <v>720</v>
+      </c>
+      <c r="C485" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D485" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E485" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G485" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="3" t="inlineStr">
+        <is>
+          <t>dating in your 50s</t>
+        </is>
+      </c>
+      <c r="B486" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="C478" s="2" t="n">
+      <c r="C486" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D486" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E486" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G486" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="3" t="inlineStr">
+        <is>
+          <t>dating after divorce</t>
+        </is>
+      </c>
+      <c r="B487" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C487" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D487" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E487" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G487" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="3" t="inlineStr">
+        <is>
+          <t>dating burnout</t>
+        </is>
+      </c>
+      <c r="B488" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="C488" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D488" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E488" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G488" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="3" t="inlineStr">
+        <is>
+          <t>online dating to relationship</t>
+        </is>
+      </c>
+      <c r="B489" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C489" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D489" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E489" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Middle of funnel</t>
+        </is>
+      </c>
+      <c r="G489" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="3" t="inlineStr">
+        <is>
+          <t>dating for professionals</t>
+        </is>
+      </c>
+      <c r="B490" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C490" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D478" s="8" t="inlineStr">
+      <c r="D490" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E478" s="12" t="inlineStr">
-        <is>
-          <t>Dating Coaching</t>
-        </is>
-      </c>
-      <c r="F478" t="inlineStr">
-        <is>
-          <t>Top of funnel</t>
-        </is>
-      </c>
-      <c r="G478" s="15" t="inlineStr">
+      <c r="E490" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Middle of funnel</t>
+        </is>
+      </c>
+      <c r="G490" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="3" t="inlineStr">
+        <is>
+          <t>texting after first date</t>
+        </is>
+      </c>
+      <c r="B491" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="C491" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D491" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E491" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G491" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="3" t="inlineStr">
+        <is>
+          <t>ghosting dating</t>
+        </is>
+      </c>
+      <c r="B492" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="C492" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D492" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E492" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G492" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="3" t="inlineStr">
+        <is>
+          <t>lasting relationship advice</t>
+        </is>
+      </c>
+      <c r="B493" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C493" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D493" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E493" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G493" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="3" t="inlineStr">
+        <is>
+          <t>dating again after a breakup</t>
+        </is>
+      </c>
+      <c r="B494" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C494" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D494" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E494" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G494" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="3" t="inlineStr">
+        <is>
+          <t>first date activities</t>
+        </is>
+      </c>
+      <c r="B495" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C495" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D495" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E495" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G495" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="3" t="inlineStr">
+        <is>
+          <t>chemistry vs compatibility</t>
+        </is>
+      </c>
+      <c r="B496" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C496" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D496" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E496" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G496" s="15" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="3" t="inlineStr">
+        <is>
+          <t>how to flirt</t>
+        </is>
+      </c>
+      <c r="B497" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C497" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D497" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E497" s="12" t="inlineStr">
+        <is>
+          <t>Dating Coaching</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Top of funnel</t>
+        </is>
+      </c>
+      <c r="G497" s="15" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -22840,9 +23467,9 @@
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  120 articles, split exactly 40/40/40 across Months 1-3
-  94,570 total monthly searches addressed
-  94 easy wins at KD &lt; 30 — front-loaded into Month 1 so you see local rankings early
-  Average difficulty KD 21.3 — deliberately achievable, weighted toward winnable local terms</t>
+  76,560 total monthly searches addressed
+  96 easy wins at KD &lt; 30 — front-loaded into Month 1 so you see local rankings early
+  Average difficulty KD 19.8 — deliberately achievable, weighted toward winnable local terms</t>
         </is>
       </c>
     </row>

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Matchmaking for Gay Singles in Los Angeles</t>
+          <t>Where Los Angeles Professionals Actually Meet Someone</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>gay matchmaker los angeles</t>
+          <t>los angeles dating scene</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>25</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>KD 3. Niche-local page, near-zero difficulty.</t>
+          <t>LA dating-scene support blog; links up to the LA location page.</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
@@ -20727,28 +20727,28 @@
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
         <is>
-          <t>gay matchmaker los angeles</t>
+          <t>los angeles dating scene</t>
         </is>
       </c>
       <c r="B431" s="4" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="C431" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D431" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E431" s="11" t="inlineStr">
-        <is>
-          <t>City Matchmaker Pages</t>
+        <v>25</v>
+      </c>
+      <c r="D431" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E431" s="10" t="inlineStr">
+        <is>
+          <t>Local Dating Guides</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Bottom of funnel</t>
+          <t>Top of funnel</t>
         </is>
       </c>
       <c r="G431" s="15" t="inlineStr">
@@ -23449,7 +23449,7 @@
     <row r="14" ht="66" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  City Matchmaker Pages   — your localization money pages: '[city] matchmaker' for metros you don't have a page for yet, plus niche-local (Jewish/gay/elite). This is the direct answer to Luma's local-page strategy.
+          <t xml:space="preserve">  City Matchmaker Pages   — your localization money pages: '[city] matchmaker' for metros you don't have a page for yet, plus niche-local (Jewish/elite/luxury). This is the direct answer to Luma's local-page strategy.
   Local Dating Guides     — 'date ideas / date night [city]' — low-difficulty local content that wins AI overviews and feeds your city pages. These are the exact terms Luma already ranks for and you don't.
   Matchmaking 101 &amp; Cost  — the buyer-decision questions ('how much does a matchmaker cost', 'are matchmakers worth it') that AI engines answer directly. Owning these puts you in the AI answer for someone choosing a matchmaker.
   Dating Coaching         — first-date, life-stage and relationship advice that builds topical authority and captures the app-fatigued searcher before they're ready to hire.</t>
@@ -23467,9 +23467,9 @@
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  120 articles, split exactly 40/40/40 across Months 1-3
-  76,560 total monthly searches addressed
+  77,150 total monthly searches addressed
   96 easy wins at KD &lt; 30 — front-loaded into Month 1 so you see local rankings early
-  Average difficulty KD 19.8 — deliberately achievable, weighted toward winnable local terms</t>
+  Average difficulty KD 20.0 — deliberately achievable, weighted toward winnable local terms</t>
         </is>
       </c>
     </row>

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in New York</t>
+          <t>New York Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Date Ideas in New York Worth Leaving the House For</t>
+          <t>New York Date Ideas Locals Actually Love</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Los Angeles</t>
+          <t>Looking for a Matchmaker in Los Angeles?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date Ideas in Los Angeles Worth Leaving the House For</t>
+          <t>Where to Take a Date in Los Angeles</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Date Night in Los Angeles: A Local Guide</t>
+          <t>Los Angeles Date Nights That Actually Impress</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Los Angeles</t>
+          <t>Los Angeles Dating, With Expert Coaching</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Chicago</t>
+          <t>Meet Your Match in Chicago</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Date Ideas in Chicago Worth Leaving the House For</t>
+          <t>The Best Date Ideas in Chicago</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Date Night in Chicago: A Local Guide</t>
+          <t>Romantic Date Nights in Chicago</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Chicago</t>
+          <t>The Chicago Dating Scene for Busy Professionals</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Chicago</t>
+          <t>How to Date Smarter in Chicago</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Dallas</t>
+          <t>How to Find a Great Matchmaker in Dallas</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Date Ideas in Dallas Worth Leaving the House For</t>
+          <t>Creative Date Ideas in Dallas</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Date Night in Dallas: A Local Guide</t>
+          <t>The Dallas Date-Night Playbook</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Dallas</t>
+          <t>How to Meet Someone in Dallas Without Swiping</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Dallas</t>
+          <t>Dating Coaching for Dallas Professionals</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Houston</t>
+          <t>Why Houston Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Date Ideas in Houston Worth Leaving the House For</t>
+          <t>Houston Date Ideas, From First Date to Fifth</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Date Night in Houston: A Local Guide</t>
+          <t>Where to Spend Date Night in Houston</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Houston</t>
+          <t>Where Houston Professionals Actually Meet</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Houston</t>
+          <t>Making Time to Date in Houston</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Washington</t>
+          <t>Your Personal Matchmaker in Washington</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Date Ideas in Washington Worth Leaving the House For</t>
+          <t>Date Ideas in Washington Beyond Dinner and a Movie</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Date Night in Washington: A Local Guide</t>
+          <t>Date Night Done Right in Washington</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Washington</t>
+          <t>A Smarter Approach to Dating in Washington</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Philadelphia</t>
+          <t>Professional Matchmaking in Philadelphia, Explained</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Date Ideas in Philadelphia Worth Leaving the House For</t>
+          <t>Fresh Date Ideas Worth Trying in Philadelphia</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Date Night in Philadelphia: A Local Guide</t>
+          <t>Philadelphia After Dark: Date-Night Ideas</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Atlanta</t>
+          <t>Is Hiring a Matchmaker Worth It in Atlanta?</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Date Ideas in Atlanta Worth Leaving the House For</t>
+          <t>Memorable Date Ideas Around Atlanta</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Date Night in Atlanta: A Local Guide</t>
+          <t>Planning the Perfect Atlanta Date Night</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Atlanta</t>
+          <t>Meeting Quality Singles in Atlanta</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Atlanta</t>
+          <t>Dating Confidently in Atlanta</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Miami</t>
+          <t>The Modern Way to Date in Miami</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Date Ideas in Miami Worth Leaving the House For</t>
+          <t>Miami Date Ideas Locals Actually Love</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Miami</t>
+          <t>Miami Dating Tips From the Experts</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Phoenix</t>
+          <t>Hand-Picked Introductions for Phoenix Singles</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Date Ideas in Phoenix Worth Leaving the House For</t>
+          <t>Where to Take a Date in Phoenix</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Date Night in Phoenix: A Local Guide</t>
+          <t>Phoenix Date Nights That Actually Impress</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Boston</t>
+          <t>Matchmaking in Boston for Busy Professionals</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Date Ideas in Boston Worth Leaving the House For</t>
+          <t>The Best Date Ideas in Boston</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Date Night in Boston: A Local Guide</t>
+          <t>Romantic Date Nights in Boston</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Boston</t>
+          <t>The Best Places to Meet Singles in Boston</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Boston</t>
+          <t>Boston Dating, With Expert Coaching</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in San Francisco</t>
+          <t>What a San Francisco Matchmaker Actually Does</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Date Ideas in San Francisco Worth Leaving the House For</t>
+          <t>Creative Date Ideas in San Francisco</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Date Night in San Francisco: A Local Guide</t>
+          <t>The San Francisco Date-Night Playbook</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in San Francisco</t>
+          <t>How to Date Smarter in San Francisco</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Detroit</t>
+          <t>Serious About Dating in Detroit? Consider a Matchmaker</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Seattle</t>
+          <t>Seattle's Alternative to Endless Swiping</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Date Ideas in Seattle Worth Leaving the House For</t>
+          <t>Seattle Date Ideas, From First Date to Fifth</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Date Night in Seattle: A Local Guide</t>
+          <t>Where to Spend Date Night in Seattle</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Seattle</t>
+          <t>Dating in Seattle: Where to Actually Meet People</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Minneapolis</t>
+          <t>Finding Love in Minneapolis, the Personal Way</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Date Ideas in Minneapolis Worth Leaving the House For</t>
+          <t>Date Ideas in Minneapolis Beyond Dinner and a Movie</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in San Diego</t>
+          <t>San Diego Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Date Ideas in San Diego Worth Leaving the House For</t>
+          <t>Fresh Date Ideas Worth Trying in San Diego</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in San Diego</t>
+          <t>How Professionals Find Their Match in San Diego</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in San Diego</t>
+          <t>Dating Coaching for San Diego Professionals</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Tampa</t>
+          <t>Looking for a Matchmaker in Tampa?</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Date Ideas in Tampa Worth Leaving the House For</t>
+          <t>Memorable Date Ideas Around Tampa</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Date Night in Tampa: A Local Guide</t>
+          <t>Date Night Done Right in Tampa</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Tampa</t>
+          <t>Making Time to Date in Tampa</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Denver</t>
+          <t>Meet Your Match in Denver</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Date Ideas in Denver Worth Leaving the House For</t>
+          <t>Denver Date Ideas Locals Actually Love</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Date Night in Denver: A Local Guide</t>
+          <t>Denver After Dark: Date-Night Ideas</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Denver</t>
+          <t>The Denver Dating Scene for Busy Professionals</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Denver</t>
+          <t>A Smarter Approach to Dating in Denver</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Baltimore</t>
+          <t>How to Find a Great Matchmaker in Baltimore</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Date Ideas in Baltimore Worth Leaving the House For</t>
+          <t>Where to Take a Date in Baltimore</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Date Night in Baltimore: A Local Guide</t>
+          <t>Planning the Perfect Baltimore Date Night</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Baltimore</t>
+          <t>Dating Confidently in Baltimore</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in St. Louis</t>
+          <t>Why St. Louis Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Date Ideas in St. Louis Worth Leaving the House For</t>
+          <t>The Best Date Ideas in St. Louis</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in St. Louis</t>
+          <t>St. Louis Dating Tips From the Experts</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Charlotte</t>
+          <t>Your Personal Matchmaker in Charlotte</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Charlotte</t>
+          <t>How to Meet Someone in Charlotte Without Swiping</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Orlando</t>
+          <t>Professional Matchmaking in Orlando, Explained</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Date Ideas in Orlando Worth Leaving the House For</t>
+          <t>Creative Date Ideas in Orlando</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Date Night in Orlando: A Local Guide</t>
+          <t>Orlando Date Nights That Actually Impress</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in San Antonio</t>
+          <t>Is Hiring a Matchmaker Worth It in San Antonio?</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Portland</t>
+          <t>The Modern Way to Date in Portland</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Sacramento</t>
+          <t>Hand-Picked Introductions for Sacramento Singles</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Pittsburgh</t>
+          <t>Matchmaking in Pittsburgh for Busy Professionals</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Las Vegas</t>
+          <t>What a Las Vegas Matchmaker Actually Does</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Cincinnati</t>
+          <t>Serious About Dating in Cincinnati? Consider a Matchmaker</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Kansas City</t>
+          <t>Kansas City's Alternative to Endless Swiping</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Columbus</t>
+          <t>Finding Love in Columbus, the Personal Way</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Cleveland</t>
+          <t>Cleveland Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Indianapolis</t>
+          <t>Looking for a Matchmaker in Indianapolis?</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Nashville</t>
+          <t>Meet Your Match in Nashville</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Milwaukee</t>
+          <t>How to Find a Great Matchmaker in Milwaukee</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Jacksonville</t>
+          <t>Why Jacksonville Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Oklahoma City</t>
+          <t>Your Personal Matchmaker in Oklahoma City</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Raleigh</t>
+          <t>Professional Matchmaking in Raleigh, Explained</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Memphis</t>
+          <t>Is Hiring a Matchmaker Worth It in Memphis?</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Richmond</t>
+          <t>The Modern Way to Date in Richmond</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in New Orleans</t>
+          <t>Hand-Picked Introductions for New Orleans Singles</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Louisville</t>
+          <t>Matchmaking in Louisville for Busy Professionals</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Buffalo</t>
+          <t>What a Buffalo Matchmaker Actually Does</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Salt Lake City</t>
+          <t>Serious About Dating in Salt Lake City? Consider a Matchmaker</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Birmingham</t>
+          <t>Birmingham's Alternative to Endless Swiping</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Tucson</t>
+          <t>Finding Love in Tucson, the Personal Way</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Tulsa</t>
+          <t>Tulsa Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Omaha</t>
+          <t>Looking for a Matchmaker in Omaha?</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Albuquerque</t>
+          <t>Meet Your Match in Albuquerque</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Knoxville</t>
+          <t>How to Find a Great Matchmaker in Knoxville</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Boise</t>
+          <t>Why Boise Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Des Moines</t>
+          <t>Your Personal Matchmaker in Des Moines</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Spokane</t>
+          <t>Professional Matchmaking in Spokane, Explained</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Reno</t>
+          <t>Is Hiring a Matchmaker Worth It in Reno?</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Find a Matchmaker in Naples</t>
+          <t>The Modern Way to Date in Naples</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meet Your Match in Chicago</t>
+          <t>How to Find a Great Matchmaker in Chicago</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Dallas</t>
+          <t>Why Dallas Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Why Houston Singles Are Turning to Matchmakers</t>
+          <t>Professional Matchmaking in Houston, Explained</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Washington</t>
+          <t>Is Hiring a Matchmaker Worth It in Washington?</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Philadelphia, Explained</t>
+          <t>Matchmaking in Philadelphia for Busy Professionals</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in Atlanta?</t>
+          <t>What an Atlanta Matchmaker Actually Does</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Modern Way to Date in Miami</t>
+          <t>Your Personal Matchmaker in Miami</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hand-Picked Introductions for Phoenix Singles</t>
+          <t>Phoenix Matchmaking, Done for You</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Matchmaking in Boston for Busy Professionals</t>
+          <t>Meet Your Match With a Boston Matchmaker</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What a San Francisco Matchmaker Actually Does</t>
+          <t>The San Francisco Matchmaker for Serious Singles</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Serious About Dating in Detroit? Consider a Matchmaker</t>
+          <t>Serious About Dating in Detroit? Meet a Matchmaker</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Seattle's Alternative to Endless Swiping</t>
+          <t>Finding Love in Seattle With a Matchmaker</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Finding Love in Minneapolis, the Personal Way</t>
+          <t>A Minneapolis Matchmaker's Take on Modern Dating</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Meet Your Match in Denver</t>
+          <t>How to Find a Great Matchmaker in Denver</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Baltimore</t>
+          <t>Why Baltimore Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Why St. Louis Singles Are Turning to Matchmakers</t>
+          <t>Professional Matchmaking in St. Louis, Explained</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Charlotte</t>
+          <t>Is Hiring a Matchmaker Worth It in Charlotte?</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Orlando, Explained</t>
+          <t>Matchmaking in Orlando for Busy Professionals</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in San Antonio?</t>
+          <t>What a San Antonio Matchmaker Actually Does</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Modern Way to Date in Portland</t>
+          <t>Your Personal Matchmaker in Portland</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hand-Picked Introductions for Sacramento Singles</t>
+          <t>Sacramento Matchmaking, Done for You</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Matchmaking in Pittsburgh for Busy Professionals</t>
+          <t>Meet Your Match With a Pittsburgh Matchmaker</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What a Las Vegas Matchmaker Actually Does</t>
+          <t>The Las Vegas Matchmaker for Serious Singles</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Serious About Dating in Cincinnati? Consider a Matchmaker</t>
+          <t>Serious About Dating in Cincinnati? Meet a Matchmaker</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kansas City's Alternative to Endless Swiping</t>
+          <t>Finding Love in Kansas City With a Matchmaker</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Finding Love in Columbus, the Personal Way</t>
+          <t>A Columbus Matchmaker's Take on Modern Dating</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Meet Your Match in Nashville</t>
+          <t>How to Find a Great Matchmaker in Nashville</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Milwaukee</t>
+          <t>Why Milwaukee Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Why Jacksonville Singles Are Turning to Matchmakers</t>
+          <t>Professional Matchmaking in Jacksonville, Explained</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Oklahoma City</t>
+          <t>Is Hiring a Matchmaker Worth It in Oklahoma City?</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Raleigh, Explained</t>
+          <t>Matchmaking in Raleigh for Busy Professionals</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in Memphis?</t>
+          <t>What a Memphis Matchmaker Actually Does</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>The Modern Way to Date in Richmond</t>
+          <t>Your Personal Matchmaker in Richmond</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hand-Picked Introductions for New Orleans Singles</t>
+          <t>New Orleans Matchmaking, Done for You</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Matchmaking in Louisville for Busy Professionals</t>
+          <t>Meet Your Match With a Louisville Matchmaker</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>What a Buffalo Matchmaker Actually Does</t>
+          <t>The Buffalo Matchmaker for Serious Singles</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Serious About Dating in Salt Lake City? Consider a Matchmaker</t>
+          <t>Serious About Dating in Salt Lake City? Meet a Matchmaker</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Birmingham's Alternative to Endless Swiping</t>
+          <t>Finding Love in Birmingham With a Matchmaker</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Finding Love in Tucson, the Personal Way</t>
+          <t>A Tucson Matchmaker's Take on Modern Dating</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Meet Your Match in Albuquerque</t>
+          <t>How to Find a Great Matchmaker in Albuquerque</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Knoxville</t>
+          <t>Why Knoxville Singles Are Turning to Matchmakers</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Why Boise Singles Are Turning to Matchmakers</t>
+          <t>Professional Matchmaking in Boise, Explained</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Des Moines</t>
+          <t>Is Hiring a Matchmaker Worth It in Des Moines?</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Spokane, Explained</t>
+          <t>Matchmaking in Spokane for Busy Professionals</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in Reno?</t>
+          <t>What a Reno Matchmaker Actually Does</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The Modern Way to Date in Naples</t>
+          <t>Your Personal Matchmaker in Naples</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Date Ideas Locals Actually Love</t>
+          <t>New York Date Ideas Locals Actually Love, Season by Season</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Date Night in New York: A Local Guide</t>
+          <t>Date Night in New York: A Local Guide to the Best Spots</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in New York</t>
+          <t>Dating for Busy Professionals in New York: Make Time for Love</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Los Angeles?</t>
+          <t>Looking for a Matchmaker in Los Angeles? Here's How to Choose</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Where to Take a Date in Los Angeles</t>
+          <t>Where to Take a Date in Los Angeles: A Local's Shortlist</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Los Angeles Date Nights That Actually Impress</t>
+          <t>Los Angeles Date Nights That Actually Impress a Date</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Los Angeles</t>
+          <t>Where to Meet Singles in Los Angeles Without the Apps</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Los Angeles Dating, With Expert Coaching</t>
+          <t>Los Angeles Dating, With Expert Coaching That Actually Helps</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Chicago</t>
+          <t>How to Find a Matchmaker in Chicago You Can Actually Trust</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Best Date Ideas in Chicago</t>
+          <t>The Best Date Ideas in Chicago for Every Kind of Couple</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Romantic Date Nights in Chicago</t>
+          <t>Romantic Date Nights in Chicago for Every Season</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Chicago Dating Scene for Busy Professionals</t>
+          <t>The Chicago Dating Scene for Busy Professionals, Decoded</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>How to Date Smarter in Chicago</t>
+          <t>How to Date Smarter in Chicago and Stop Wasting Time</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Why Dallas Singles Are Turning to Matchmakers</t>
+          <t>Why Dallas Singles Are Choosing Professional Matchmakers</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creative Date Ideas in Dallas</t>
+          <t>Creative Date Ideas in Dallas Beyond Dinner and a Movie</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Dallas Date-Night Playbook</t>
+          <t>The Dallas Date-Night Playbook, From Casual to Elegant</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>How to Meet Someone in Dallas Without Swiping</t>
+          <t>How to Meet Someone in Dallas When Swiping Isn't Working</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dating Coaching for Dallas Professionals</t>
+          <t>Dating Coaching for Dallas Professionals Who Are Serious</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Houston, Explained</t>
+          <t>Professional Matchmaking in Houston: What to Expect</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Houston Date Ideas, From First Date to Fifth</t>
+          <t>Houston Date Ideas, From a Casual First Date to the Fifth</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Where to Spend Date Night in Houston</t>
+          <t>Where to Spend Date Night in Houston Without the Guesswork</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Where Houston Professionals Actually Meet</t>
+          <t>Where Houston Professionals Actually Meet Their Match</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Making Time to Date in Houston</t>
+          <t>Making Time to Date in Houston When Life Is Busy</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in Washington?</t>
+          <t>Is Hiring a Matchmaker in Washington Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Date Ideas in Washington Beyond Dinner and a Movie</t>
+          <t>Date Ideas in Washington That Actually Lead Somewhere</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Date Night Done Right in Washington</t>
+          <t>Date Night Done Right in Washington: Ideas That Land</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A Smarter Approach to Dating in Washington</t>
+          <t>A Smarter Approach to Dating in Washington for Professionals</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Matchmaking in Philadelphia for Busy Professionals</t>
+          <t>What a Philadelphia Matchmaker Does That Dating Apps Can't</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fresh Date Ideas Worth Trying in Philadelphia</t>
+          <t>Fresh Philadelphia Date Ideas Worth Leaving the House For</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Philadelphia After Dark: Date-Night Ideas</t>
+          <t>Philadelphia After Dark: Date-Night Ideas Worth Planning</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What an Atlanta Matchmaker Actually Does</t>
+          <t>Your Personal Matchmaker in Atlanta: Introductions Done Right</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Memorable Date Ideas Around Atlanta</t>
+          <t>Memorable Date Ideas Around Atlanta for Any Budget</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Planning the Perfect Atlanta Date Night</t>
+          <t>Planning the Perfect Date Night in Atlanta</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Meeting Quality Singles in Atlanta</t>
+          <t>Meeting Quality Singles in Atlanta: A Practical Guide</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dating Confidently in Atlanta</t>
+          <t>Dating Confidently in Atlanta: Advice From the Experts</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Miami</t>
+          <t>Miami Matchmaking, Done for You From Vetting to First Date</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Miami Date Ideas Locals Actually Love</t>
+          <t>Miami Date Ideas Locals Actually Love, Season by Season</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Date Night in Miami: A Local Guide</t>
+          <t>Date Night in Miami: A Local Guide to the Best Spots</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Miami Dating Tips From the Experts</t>
+          <t>Miami Dating Tips From Professional Matchmakers</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Phoenix Matchmaking, Done for You</t>
+          <t>Meet Someone Worth Your Time With a Phoenix Matchmaker</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Where to Take a Date in Phoenix</t>
+          <t>Where to Take a Date in Phoenix: A Local's Shortlist</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Phoenix Date Nights That Actually Impress</t>
+          <t>Phoenix Date Nights That Actually Impress a Date</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Phoenix</t>
+          <t>Dating for Busy Professionals in Phoenix: Make Time for Love</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Meet Your Match With a Boston Matchmaker</t>
+          <t>The Boston Matchmaker for Marriage-Minded Professionals</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Best Date Ideas in Boston</t>
+          <t>The Best Date Ideas in Boston for Every Kind of Couple</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Romantic Date Nights in Boston</t>
+          <t>Romantic Date Nights in Boston for Every Season</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Best Places to Meet Singles in Boston</t>
+          <t>The Best Places to Meet Singles in Boston in Real Life</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Boston Dating, With Expert Coaching</t>
+          <t>Boston Dating, With Expert Coaching That Actually Helps</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The San Francisco Matchmaker for Serious Singles</t>
+          <t>Serious About Dating in San Francisco? A Matchmaker Can Help</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Creative Date Ideas in San Francisco</t>
+          <t>Creative Date Ideas in San Francisco Beyond Dinner and a Movie</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The San Francisco Date-Night Playbook</t>
+          <t>The San Francisco Date-Night Playbook, From Casual to Elegant</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How to Date Smarter in San Francisco</t>
+          <t>How to Date Smarter in San Francisco and Stop Wasting Time</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Serious About Dating in Detroit? Meet a Matchmaker</t>
+          <t>Finding Love in Detroit With a Professional Matchmaker</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Finding Love in Seattle With a Matchmaker</t>
+          <t>A Seattle Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Seattle Date Ideas, From First Date to Fifth</t>
+          <t>Seattle Date Ideas, From a Casual First Date to the Fifth</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Where to Spend Date Night in Seattle</t>
+          <t>Where to Spend Date Night in Seattle Without the Guesswork</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dating in Seattle: Where to Actually Meet People</t>
+          <t>Dating in Seattle: Where to Actually Meet Real People</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A Minneapolis Matchmaker's Take on Modern Dating</t>
+          <t>Minneapolis Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Date Ideas in Minneapolis Beyond Dinner and a Movie</t>
+          <t>Date Ideas in Minneapolis That Actually Lead Somewhere</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>San Diego Matchmaker: How Personalized Matchmaking Works</t>
+          <t>Looking for a Matchmaker in San Diego? Here's How to Choose</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fresh Date Ideas Worth Trying in San Diego</t>
+          <t>Fresh San Diego Date Ideas Worth Leaving the House For</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dating Coaching for San Diego Professionals</t>
+          <t>Dating Coaching for San Diego Professionals Who Are Serious</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Tampa?</t>
+          <t>How to Find a Matchmaker in Tampa You Can Actually Trust</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Memorable Date Ideas Around Tampa</t>
+          <t>Memorable Date Ideas Around Tampa for Any Budget</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Date Night Done Right in Tampa</t>
+          <t>Date Night Done Right in Tampa: Ideas That Land</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Where to Meet Singles in Tampa</t>
+          <t>Where to Meet Singles in Tampa Without the Apps</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Making Time to Date in Tampa</t>
+          <t>Making Time to Date in Tampa When Life Is Busy</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Denver</t>
+          <t>Why Denver Singles Are Choosing Professional Matchmakers</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Denver Date Ideas Locals Actually Love</t>
+          <t>Denver Date Ideas Locals Actually Love, Season by Season</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Denver After Dark: Date-Night Ideas</t>
+          <t>Denver After Dark: Date-Night Ideas Worth Planning</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Denver Dating Scene for Busy Professionals</t>
+          <t>The Denver Dating Scene for Busy Professionals, Decoded</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A Smarter Approach to Dating in Denver</t>
+          <t>A Smarter Approach to Dating in Denver for Professionals</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Why Baltimore Singles Are Turning to Matchmakers</t>
+          <t>Professional Matchmaking in Baltimore: What to Expect</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Where to Take a Date in Baltimore</t>
+          <t>Where to Take a Date in Baltimore: A Local's Shortlist</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Planning the Perfect Baltimore Date Night</t>
+          <t>Planning the Perfect Date Night in Baltimore</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dating Confidently in Baltimore</t>
+          <t>Dating Confidently in Baltimore: Advice From the Experts</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in St. Louis, Explained</t>
+          <t>Is Hiring a Matchmaker in St. Louis Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Best Date Ideas in St. Louis</t>
+          <t>The Best Date Ideas in St. Louis for Every Kind of Couple</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Date Night in St. Louis: A Local Guide</t>
+          <t>Date Night in St. Louis: A Local Guide to the Best Spots</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>St. Louis Dating Tips From the Experts</t>
+          <t>St. Louis Dating Tips From Professional Matchmakers</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in Charlotte?</t>
+          <t>Matchmaking in Charlotte for Busy, Relationship-Ready Singles</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>How to Meet Someone in Charlotte Without Swiping</t>
+          <t>How to Meet Someone in Charlotte When Swiping Isn't Working</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dating for Busy Professionals in Charlotte</t>
+          <t>Dating for Busy Professionals in Charlotte: Make Time for Love</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Matchmaking in Orlando for Busy Professionals</t>
+          <t>What an Orlando Matchmaker Does That Dating Apps Can't</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Creative Date Ideas in Orlando</t>
+          <t>Creative Date Ideas in Orlando Beyond Dinner and a Movie</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Orlando Date Nights That Actually Impress</t>
+          <t>Orlando Date Nights That Actually Impress a Date</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What a San Antonio Matchmaker Actually Does</t>
+          <t>Meet Someone Worth Your Time With a San Antonio Matchmaker</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Portland</t>
+          <t>The Portland Matchmaker for Marriage-Minded Professionals</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sacramento Matchmaking, Done for You</t>
+          <t>Serious About Dating in Sacramento? A Matchmaker Can Help</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Meet Your Match With a Pittsburgh Matchmaker</t>
+          <t>Finding Love in Pittsburgh With a Professional Matchmaker</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Las Vegas Matchmaker for Serious Singles</t>
+          <t>A Las Vegas Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Serious About Dating in Cincinnati? Meet a Matchmaker</t>
+          <t>Cincinnati Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Finding Love in Kansas City With a Matchmaker</t>
+          <t>Looking for a Matchmaker in Kansas City? Here's How to Choose</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>A Columbus Matchmaker's Take on Modern Dating</t>
+          <t>How to Find a Matchmaker in Columbus You Can Actually Trust</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cleveland Matchmaker: How Personalized Matchmaking Works</t>
+          <t>Why Cleveland Singles Are Choosing Professional Matchmakers</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Indianapolis?</t>
+          <t>Professional Matchmaking in Indianapolis: What to Expect</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Nashville</t>
+          <t>Is Hiring a Matchmaker in Nashville Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Why Milwaukee Singles Are Turning to Matchmakers</t>
+          <t>Matchmaking in Milwaukee for Busy, Relationship-Ready Singles</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Jacksonville, Explained</t>
+          <t>What a Jacksonville Matchmaker Does That Dating Apps Can't</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in Oklahoma City?</t>
+          <t>Meet Someone Worth Your Time With an Oklahoma City Matchmaker</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Matchmaking in Raleigh for Busy Professionals</t>
+          <t>The Raleigh Matchmaker for Marriage-Minded Professionals</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What a Memphis Matchmaker Actually Does</t>
+          <t>Serious About Dating in Memphis? A Matchmaker Can Help</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Richmond</t>
+          <t>Finding Love in Richmond With a Professional Matchmaker</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>New Orleans Matchmaking, Done for You</t>
+          <t>A New Orleans Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Meet Your Match With a Louisville Matchmaker</t>
+          <t>Louisville Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Buffalo Matchmaker for Serious Singles</t>
+          <t>Looking for a Matchmaker in Buffalo? Here's How to Choose</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Serious About Dating in Salt Lake City? Meet a Matchmaker</t>
+          <t>Professional Matchmaking in Salt Lake City: What to Expect</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Finding Love in Birmingham With a Matchmaker</t>
+          <t>Is Hiring a Matchmaker in Birmingham Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A Tucson Matchmaker's Take on Modern Dating</t>
+          <t>Matchmaking in Tucson for Busy, Relationship-Ready Singles</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tulsa Matchmaker: How Personalized Matchmaking Works</t>
+          <t>What a Tulsa Matchmaker Does That Dating Apps Can't</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Omaha?</t>
+          <t>Your Personal Matchmaker in Omaha: Introductions Done Right</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>How to Find a Great Matchmaker in Albuquerque</t>
+          <t>Meet Someone Worth Your Time With an Albuquerque Matchmaker</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Why Knoxville Singles Are Turning to Matchmakers</t>
+          <t>The Knoxville Matchmaker for Marriage-Minded Professionals</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Boise, Explained</t>
+          <t>Serious About Dating in Boise? A Matchmaker Can Help</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker Worth It in Des Moines?</t>
+          <t>Finding Love in Des Moines With a Professional Matchmaker</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Matchmaking in Spokane for Busy Professionals</t>
+          <t>A Spokane Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What a Reno Matchmaker Actually Does</t>
+          <t>Reno Matchmaker: How Personalized Matchmaking Works</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Naples</t>
+          <t>Looking for a Matchmaker in Naples? Here's How to Choose</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker in Washington Worth It? An Honest Take</t>
+          <t>Is Hiring a Matchmaker in DC Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Date Ideas in Washington That Actually Lead Somewhere</t>
+          <t>Date Ideas in Washington, DC That Actually Lead Somewhere</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Date Night Done Right in Washington: Ideas That Land</t>
+          <t>Date Night Done Right in Washington, DC: Ideas That Land</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A Smarter Approach to Dating in Washington for Professionals</t>
+          <t>A Smarter Approach to Dating in DC for Professionals</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -4999,18 +4999,18 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>cara matchmaking portland me</t>
+          <t>portland matchmaker</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>15</v>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Portland (2.5M metro) — links up to the Portland location page.</t>
+          <t>Portland (2.5M metro) — clean 'portland matchmaker' (Portland OR); replaced bad kw 'cara matchmaking portland me' (Portland ME + competitor brand).</t>
         </is>
       </c>
     </row>
@@ -22377,18 +22377,18 @@
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
         <is>
-          <t>cara matchmaking portland me</t>
+          <t>portland matchmaker</t>
         </is>
       </c>
       <c r="B481" s="4" t="n">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="C481" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D481" s="9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>15</v>
+      </c>
+      <c r="D481" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E481" s="6" t="inlineStr">
@@ -23930,7 +23930,7 @@
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  120 articles, split exactly 40/40/40 across Months 1-3
-  36,700 total monthly searches addressed
+  36,910 total monthly searches addressed
   114 easy wins at KD &lt; 30 — front-loaded into Month 1 so you see local rankings early
   Average difficulty KD 16.0 — deliberately achievable, weighted toward winnable local terms</t>
         </is>

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Finding Love in Detroit With a Professional Matchmaker</t>
+          <t>How to Find a Matchmaker in Detroit You Can Actually Trust</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Serious About Dating in Sacramento? A Matchmaker Can Help</t>
+          <t>The Sacramento Matchmaker for Marriage-Minded Professionals</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Finding Love in Pittsburgh With a Professional Matchmaker</t>
+          <t>Meet Someone Worth Your Time With a Pittsburgh Matchmaker</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Why Cleveland Singles Are Choosing Professional Matchmakers</t>
+          <t>What a Cleveland Matchmaker Does That Dating Apps Can't</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Serious About Dating in Memphis? A Matchmaker Can Help</t>
+          <t>A Memphis Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Finding Love in Richmond With a Professional Matchmaker</t>
+          <t>Is a Richmond Matchmaker Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Serious About Dating in Boise? A Matchmaker Can Help</t>
+          <t>Is a Boise Matchmaker Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Finding Love in Des Moines With a Professional Matchmaker</t>
+          <t>How to Find a Matchmaker in Des Moines You Can Actually Trust</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -5190,12 +5190,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cincinnati Matchmaker: How Personalized Matchmaking Works</t>
+          <t>Looking for a Matchmaker in Kansas City? Here's How to Choose</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>cincinnati matchmaker</t>
+          <t>kansas city matchmaker</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Cincinnati (2.3M metro) — links up to the Cincinnati location page.</t>
+          <t>Kansas City (2.2M metro) — links up to the Kansas City location page.</t>
         </is>
       </c>
     </row>
@@ -5239,19 +5239,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Kansas City? Here's How to Choose</t>
+          <t>How to Find a Matchmaker in Columbus You Can Actually Trust</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>kansas city matchmaker</t>
+          <t>matchmaker columbus ohio</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>Kansas City (2.2M metro) — links up to the Kansas City location page.</t>
+          <t>Columbus (2.1M metro) — links up to the Columbus location page.</t>
         </is>
       </c>
     </row>
@@ -5288,19 +5288,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>How to Find a Matchmaker in Columbus You Can Actually Trust</t>
+          <t>Professional Matchmaking in Indianapolis: What to Expect</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>matchmaker columbus ohio</t>
+          <t>indianapolis matchmaker</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Columbus (2.1M metro) — links up to the Columbus location page.</t>
+          <t>Indianapolis (2.1M metro) — links up to the Indianapolis location page.</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What a Cleveland Matchmaker Does That Dating Apps Can't</t>
+          <t>Is Hiring a Matchmaker in Nashville Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>cleveland matchmaker</t>
+          <t>nashville matchmaker</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Cleveland (2.1M metro) — links up to the Cleveland location page.</t>
+          <t>Nashville (2.0M metro) — links up to the Nashville location page.</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Indianapolis: What to Expect</t>
+          <t>What a Jacksonville Matchmaker Does That Dating Apps Can't</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>indianapolis matchmaker</t>
+          <t>jacksonville matchmaker</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Indianapolis (2.1M metro) — links up to the Indianapolis location page.</t>
+          <t>Jacksonville (1.6M metro) — links up to the Jacksonville location page.</t>
         </is>
       </c>
     </row>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker in Nashville Worth It? An Honest Take</t>
+          <t>Meet Someone Worth Your Time With an Oklahoma City Matchmaker</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>nashville matchmaker</t>
+          <t>oklahoma city matchmaker</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>Nashville (2.0M metro) — links up to the Nashville location page.</t>
+          <t>Oklahoma City (1.4M metro) — links up to the Oklahoma City location page.</t>
         </is>
       </c>
     </row>
@@ -5484,19 +5484,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Matchmaking in Milwaukee for Busy, Relationship-Ready Singles</t>
+          <t>A Memphis Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>milwaukee matchmaker</t>
+          <t>matchmaker memphis</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>Milwaukee (1.6M metro) — links up to the Milwaukee location page.</t>
+          <t>Memphis (1.3M metro) — links up to the Memphis location page.</t>
         </is>
       </c>
     </row>
@@ -5533,12 +5533,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>What a Jacksonville Matchmaker Does That Dating Apps Can't</t>
+          <t>Is a Richmond Matchmaker Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>jacksonville matchmaker</t>
+          <t>richmond matchmaker</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>Jacksonville (1.6M metro) — links up to the Jacksonville location page.</t>
+          <t>Richmond (1.3M metro) — links up to the Richmond location page.</t>
         </is>
       </c>
     </row>
@@ -5582,19 +5582,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Meet Someone Worth Your Time With an Oklahoma City Matchmaker</t>
+          <t>A New Orleans Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>oklahoma city matchmaker</t>
+          <t>new orleans matchmaker</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>Oklahoma City (1.4M metro) — links up to the Oklahoma City location page.</t>
+          <t>New Orleans (1.3M metro) — links up to the New Orleans location page.</t>
         </is>
       </c>
     </row>
@@ -5631,19 +5631,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>The Raleigh Matchmaker for Marriage-Minded Professionals</t>
+          <t>Professional Matchmaking in Salt Lake City: What to Expect</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>raleigh matchmaker</t>
+          <t>matchmaker salt lake city</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Raleigh (1.4M metro) — links up to the Raleigh location page.</t>
+          <t>Salt Lake City (1.2M metro) — links up to the Salt Lake City location page.</t>
         </is>
       </c>
     </row>
@@ -5680,19 +5680,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A Memphis Matchmaker's Approach to Intentional Dating</t>
+          <t>Looking for a Matchmaker in Naples? Here's How to Choose</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>matchmaker memphis</t>
+          <t>naples matchmaker</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>Memphis (1.3M metro) — links up to the Memphis location page.</t>
+          <t>Naples (0.38M metro) — links up to the Naples location page.</t>
         </is>
       </c>
     </row>
@@ -5729,19 +5729,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Is a Richmond Matchmaker Worth It? An Honest Take</t>
+          <t>Beverly Hills Matchmaker: Discreet, High-End Introductions</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>richmond matchmaker</t>
+          <t>beverly hills matchmaker</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>Richmond (1.3M metro) — links up to the Richmond location page.</t>
+          <t>Beverly Hills (affluent enclave) — links up to the Los Angeles metro.</t>
         </is>
       </c>
     </row>
@@ -5778,19 +5778,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A New Orleans Matchmaker's Approach to Intentional Dating</t>
+          <t>Looking for a Matchmaker in Malibu?</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>new orleans matchmaker</t>
+          <t>malibu matchmaker</t>
         </is>
       </c>
       <c r="D107" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>New Orleans (1.3M metro) — links up to the New Orleans location page.</t>
+          <t>Malibu (affluent enclave) — links up to the Los Angeles metro.</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Louisville Matchmaker: How Personalized Matchmaking Works</t>
+          <t>Your Personal Matchmaker in Newport Beach</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>louisville matchmaker</t>
+          <t>newport beach matchmaker</t>
         </is>
       </c>
       <c r="D108" s="4" t="n">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>Louisville (1.3M metro) — links up to the Louisville location page.</t>
+          <t>Newport Beach (affluent enclave) — links up to the Los Angeles metro / California state.</t>
         </is>
       </c>
     </row>
@@ -5876,19 +5876,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Buffalo? Here's How to Choose</t>
+          <t>San Jose Matchmaking for Discerning Singles</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>buffalo matchmaker</t>
+          <t>matchmaker san jose</t>
         </is>
       </c>
       <c r="D109" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>Buffalo (1.2M metro) — links up to the Buffalo location page.</t>
+          <t>San Jose (affluent enclave) — links up to the San Francisco / Bay Area metro.</t>
         </is>
       </c>
     </row>
@@ -5925,19 +5925,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Salt Lake City: What to Expect</t>
+          <t>How to Find a Matchmaker in Palo Alto You Can Trust</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>matchmaker salt lake city</t>
+          <t>palo alto matchmaker</t>
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City (1.2M metro) — links up to the Salt Lake City location page.</t>
+          <t>Palo Alto (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker in Birmingham Worth It? An Honest Take</t>
+          <t>The Atherton Matchmaker for Marriage-Minded Singles</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>birmingham matchmaker</t>
+          <t>atherton matchmaker</t>
         </is>
       </c>
       <c r="D111" s="4" t="n">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>Birmingham (1.1M metro) — links up to the Birmingham location page.</t>
+          <t>Atherton (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -6023,19 +6023,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Matchmaking in Tucson for Busy, Relationship-Ready Singles</t>
+          <t>Meet Your Match With a Hillsborough Matchmaker</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>matchmaker tucson</t>
+          <t>hillsborough matchmaker</t>
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>Tucson (1.05M metro) — links up to the Tucson location page.</t>
+          <t>Hillsborough (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -6072,19 +6072,19 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>What a Tulsa Matchmaker Does That Dating Apps Can't</t>
+          <t>Elite Matchmaking in Los Altos, Done for You</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>tulsa matchmaker</t>
+          <t>los altos matchmaker</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>Tulsa (1.02M metro) — links up to the Tulsa location page.</t>
+          <t>Los Altos (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -6121,19 +6121,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Omaha: Introductions Done Right</t>
+          <t>Scarsdale Matchmaker: Discreet, High-End Introductions</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>omaha matchmaker</t>
+          <t>scarsdale matchmaker</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>Omaha (0.97M metro) — links up to the Omaha location page.</t>
+          <t>Scarsdale (affluent enclave) — links up to the New York metro.</t>
         </is>
       </c>
     </row>
@@ -6170,19 +6170,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Meet Someone Worth Your Time With an Albuquerque Matchmaker</t>
+          <t>Looking for a Matchmaker in the Hamptons?</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>matchmaker albuquerque</t>
+          <t>hamptons matchmaker</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Albuquerque (0.92M metro) — links up to the Albuquerque location page.</t>
+          <t>Hamptons (affluent enclave) — links up to the New York metro.</t>
         </is>
       </c>
     </row>
@@ -6219,12 +6219,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>The Knoxville Matchmaker for Marriage-Minded Professionals</t>
+          <t>Your Personal Matchmaker in Greenwich</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>knoxville matchmaker</t>
+          <t>greenwich matchmaker</t>
         </is>
       </c>
       <c r="D116" s="4" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Knoxville (0.87M metro) — links up to the Knoxville location page.</t>
+          <t>Greenwich (affluent enclave) — links up to the New York metro / Connecticut state.</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Is a Boise Matchmaker Worth It? An Honest Take</t>
+          <t>Darien Matchmaking for Discerning Singles</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>boise matchmaker</t>
+          <t>darien matchmaker</t>
         </is>
       </c>
       <c r="D117" s="4" t="n">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Boise (0.76M metro) — links up to the Boise location page.</t>
+          <t>Darien (affluent enclave) — links up to the New York metro / Connecticut state.</t>
         </is>
       </c>
     </row>
@@ -6317,12 +6317,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>How to Find a Matchmaker in Des Moines You Can Actually Trust</t>
+          <t>How to Find a Matchmaker in Short Hills You Can Trust</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>des moines matchmaker</t>
+          <t>short hills matchmaker</t>
         </is>
       </c>
       <c r="D118" s="4" t="n">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>Des Moines (0.71M metro) — links up to the Des Moines location page.</t>
+          <t>Short Hills (affluent enclave) — links up to the New York metro / New Jersey state.</t>
         </is>
       </c>
     </row>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>A Spokane Matchmaker's Approach to Intentional Dating</t>
+          <t>The McLean Matchmaker for Marriage-Minded Singles</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>spokane matchmaker</t>
+          <t>mclean matchmaker</t>
         </is>
       </c>
       <c r="D119" s="4" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Spokane (0.6M metro) — links up to the Spokane location page.</t>
+          <t>McLean (affluent enclave) — links up to the Washington DC metro / Virginia state.</t>
         </is>
       </c>
     </row>
@@ -6415,12 +6415,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Reno Matchmaker: How Personalized Matchmaking Works</t>
+          <t>Meet Your Match With a Boca Raton Matchmaker</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>reno matchmaker</t>
+          <t>boca raton matchmaker</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Reno (0.49M metro) — links up to the Reno location page.</t>
+          <t>Boca Raton (affluent enclave) — links up to the Miami metro / Florida state.</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Naples? Here's How to Choose</t>
+          <t>Elite Matchmaking in Park City, Done for You</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>naples matchmaker</t>
+          <t>park city matchmaker</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>Naples (0.38M metro) — links up to the Naples location page.</t>
+          <t>Park City (affluent enclave) — links up to the Salt Lake City metro / Utah state.</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>cincinnati matchmaker</t>
+          <t>kansas city matchmaker</t>
         </is>
       </c>
       <c r="B485" s="4" t="n">
@@ -22542,14 +22542,14 @@
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>kansas city matchmaker</t>
+          <t>matchmaker columbus ohio</t>
         </is>
       </c>
       <c r="B486" s="4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C486" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D486" s="10" t="inlineStr">
         <is>
@@ -22575,14 +22575,14 @@
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>matchmaker columbus ohio</t>
+          <t>indianapolis matchmaker</t>
         </is>
       </c>
       <c r="B487" s="4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C487" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D487" s="10" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>cleveland matchmaker</t>
+          <t>nashville matchmaker</t>
         </is>
       </c>
       <c r="B488" s="4" t="n">
@@ -22641,7 +22641,7 @@
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>indianapolis matchmaker</t>
+          <t>jacksonville matchmaker</t>
         </is>
       </c>
       <c r="B489" s="4" t="n">
@@ -22674,7 +22674,7 @@
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>nashville matchmaker</t>
+          <t>oklahoma city matchmaker</t>
         </is>
       </c>
       <c r="B490" s="4" t="n">
@@ -22707,14 +22707,14 @@
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
         <is>
-          <t>milwaukee matchmaker</t>
+          <t>matchmaker memphis</t>
         </is>
       </c>
       <c r="B491" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C491" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D491" s="10" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>jacksonville matchmaker</t>
+          <t>richmond matchmaker</t>
         </is>
       </c>
       <c r="B492" s="4" t="n">
@@ -22773,14 +22773,14 @@
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
         <is>
-          <t>oklahoma city matchmaker</t>
+          <t>new orleans matchmaker</t>
         </is>
       </c>
       <c r="B493" s="4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C493" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D493" s="10" t="inlineStr">
         <is>
@@ -22806,14 +22806,14 @@
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>raleigh matchmaker</t>
+          <t>matchmaker salt lake city</t>
         </is>
       </c>
       <c r="B494" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C494" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D494" s="10" t="inlineStr">
         <is>
@@ -22839,14 +22839,14 @@
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
         <is>
-          <t>matchmaker memphis</t>
+          <t>naples matchmaker</t>
         </is>
       </c>
       <c r="B495" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C495" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D495" s="10" t="inlineStr">
         <is>
@@ -22872,14 +22872,14 @@
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>richmond matchmaker</t>
+          <t>beverly hills matchmaker</t>
         </is>
       </c>
       <c r="B496" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C496" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D496" s="10" t="inlineStr">
         <is>
@@ -22905,14 +22905,14 @@
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
         <is>
-          <t>new orleans matchmaker</t>
+          <t>malibu matchmaker</t>
         </is>
       </c>
       <c r="B497" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C497" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D497" s="10" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
         <is>
-          <t>louisville matchmaker</t>
+          <t>newport beach matchmaker</t>
         </is>
       </c>
       <c r="B498" s="4" t="n">
@@ -22971,14 +22971,14 @@
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
         <is>
-          <t>buffalo matchmaker</t>
+          <t>matchmaker san jose</t>
         </is>
       </c>
       <c r="B499" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C499" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D499" s="10" t="inlineStr">
         <is>
@@ -23004,14 +23004,14 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>matchmaker salt lake city</t>
+          <t>palo alto matchmaker</t>
         </is>
       </c>
       <c r="B500" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C500" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D500" s="10" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
         <is>
-          <t>birmingham matchmaker</t>
+          <t>atherton matchmaker</t>
         </is>
       </c>
       <c r="B501" s="4" t="n">
@@ -23070,14 +23070,14 @@
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
         <is>
-          <t>matchmaker tucson</t>
+          <t>hillsborough matchmaker</t>
         </is>
       </c>
       <c r="B502" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C502" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D502" s="10" t="inlineStr">
         <is>
@@ -23103,14 +23103,14 @@
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
         <is>
-          <t>tulsa matchmaker</t>
+          <t>los altos matchmaker</t>
         </is>
       </c>
       <c r="B503" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C503" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D503" s="10" t="inlineStr">
         <is>
@@ -23136,14 +23136,14 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>omaha matchmaker</t>
+          <t>scarsdale matchmaker</t>
         </is>
       </c>
       <c r="B504" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C504" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D504" s="10" t="inlineStr">
         <is>
@@ -23169,14 +23169,14 @@
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
         <is>
-          <t>matchmaker albuquerque</t>
+          <t>hamptons matchmaker</t>
         </is>
       </c>
       <c r="B505" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C505" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D505" s="10" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>knoxville matchmaker</t>
+          <t>greenwich matchmaker</t>
         </is>
       </c>
       <c r="B506" s="4" t="n">
@@ -23235,7 +23235,7 @@
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>boise matchmaker</t>
+          <t>darien matchmaker</t>
         </is>
       </c>
       <c r="B507" s="4" t="n">
@@ -23268,7 +23268,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>des moines matchmaker</t>
+          <t>short hills matchmaker</t>
         </is>
       </c>
       <c r="B508" s="4" t="n">
@@ -23301,7 +23301,7 @@
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>spokane matchmaker</t>
+          <t>mclean matchmaker</t>
         </is>
       </c>
       <c r="B509" s="4" t="n">
@@ -23334,7 +23334,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>reno matchmaker</t>
+          <t>boca raton matchmaker</t>
         </is>
       </c>
       <c r="B510" s="4" t="n">
@@ -23367,7 +23367,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>naples matchmaker</t>
+          <t>park city matchmaker</t>
         </is>
       </c>
       <c r="B511" s="4" t="n">
@@ -23830,7 +23830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="114" customWidth="1" min="1" max="1"/>
@@ -23930,7 +23930,7 @@
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  120 articles, split exactly 40/40/40 across Months 1-3
-  36,910 total monthly searches addressed
+  36,870 total monthly searches addressed
   114 easy wins at KD &lt; 30 — front-loaded into Month 1 so you see local rankings early
   Average difficulty KD 16.0 — deliberately achievable, weighted toward winnable local terms</t>
         </is>
@@ -23939,12 +23939,31 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
+          <t>Why some cities show low or zero search volume (and why that's fine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="98" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>You'll notice the smaller metros show low or even zero measurable monthly searches. That's expected — matchmaking is a
+niche, so most cities only have real search demand for one term: '[city] matchmaker.' These pages aren't a traffic play;
+they're a local-presence and AI-citation play — being the name that comes up when someone asks Google's AI or ChatGPT
+'who's a matchmaker in [city]?', and holding the local map spot. Depth follows demand: the biggest metros get a full
+cluster of pages, the smallest get one focused, fully-optimized page. Every city you serve is covered — we simply size
+each city's content to its actual demand so the budget goes where the return is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>What we excluded, and why</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>See the 'Excluded' sheet. The big buckets: generic non-local listicle terms ('date night ideas', 450K vol, zero buyer
 intent), dating-app and free-tool searches (your buyer has left apps behind), TV-show entertainment searches
@@ -23952,15 +23971,15 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Next step</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Approve the 120-article plan and ClusterMagic begins the Month 1 batch within 5 business days. Articles are
 entity-rich, internally linked, schema-marked, and shipped to your CMS as drafts for review — built to win both

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -5043,23 +5043,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Sacramento Matchmaker for Marriage-Minded Professionals</t>
+          <t>Meet Someone Worth Your Time With a Pittsburgh Matchmaker</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>sacramento matchmaker</t>
+          <t>pittsburgh matchmaker</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>29</v>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>Sacramento (2.4M metro) — links up to the Sacramento location page.</t>
+          <t>Pittsburgh (2.3M metro) — links up to the Pittsburgh location page.</t>
         </is>
       </c>
     </row>
@@ -5092,23 +5092,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Meet Someone Worth Your Time With a Pittsburgh Matchmaker</t>
+          <t>A Las Vegas Matchmaker's Approach to Intentional Dating</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>pittsburgh matchmaker</t>
+          <t>las vegas matchmaker</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>15</v>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Pittsburgh (2.3M metro) — links up to the Pittsburgh location page.</t>
+          <t>Las Vegas (2.3M metro) — links up to the Las Vegas location page.</t>
         </is>
       </c>
     </row>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A Las Vegas Matchmaker's Approach to Intentional Dating</t>
+          <t>Looking for a Matchmaker in Kansas City? Here's How to Choose</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>las vegas matchmaker</t>
+          <t>kansas city matchmaker</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>Las Vegas (2.3M metro) — links up to the Las Vegas location page.</t>
+          <t>Kansas City (2.2M metro) — links up to the Kansas City location page.</t>
         </is>
       </c>
     </row>
@@ -5190,19 +5190,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Kansas City? Here's How to Choose</t>
+          <t>How to Find a Matchmaker in Columbus You Can Actually Trust</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>kansas city matchmaker</t>
+          <t>matchmaker columbus ohio</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Kansas City (2.2M metro) — links up to the Kansas City location page.</t>
+          <t>Columbus (2.1M metro) — links up to the Columbus location page.</t>
         </is>
       </c>
     </row>
@@ -5239,19 +5239,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>How to Find a Matchmaker in Columbus You Can Actually Trust</t>
+          <t>Professional Matchmaking in Indianapolis: What to Expect</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>matchmaker columbus ohio</t>
+          <t>indianapolis matchmaker</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>Columbus (2.1M metro) — links up to the Columbus location page.</t>
+          <t>Indianapolis (2.1M metro) — links up to the Indianapolis location page.</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Indianapolis: What to Expect</t>
+          <t>Is Hiring a Matchmaker in Nashville Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>indianapolis matchmaker</t>
+          <t>nashville matchmaker</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Indianapolis (2.1M metro) — links up to the Indianapolis location page.</t>
+          <t>Nashville (2.0M metro) — links up to the Nashville location page.</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Is Hiring a Matchmaker in Nashville Worth It? An Honest Take</t>
+          <t>What a Jacksonville Matchmaker Does That Dating Apps Can't</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>nashville matchmaker</t>
+          <t>jacksonville matchmaker</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Nashville (2.0M metro) — links up to the Nashville location page.</t>
+          <t>Jacksonville (1.6M metro) — links up to the Jacksonville location page.</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What a Jacksonville Matchmaker Does That Dating Apps Can't</t>
+          <t>Is a Richmond Matchmaker Worth It? An Honest Take</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>jacksonville matchmaker</t>
+          <t>richmond matchmaker</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>Jacksonville (1.6M metro) — links up to the Jacksonville location page.</t>
+          <t>Richmond (1.3M metro) — links up to the Richmond location page.</t>
         </is>
       </c>
     </row>
@@ -5435,19 +5435,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Meet Someone Worth Your Time With an Oklahoma City Matchmaker</t>
+          <t>Professional Matchmaking in Salt Lake City: What to Expect</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>oklahoma city matchmaker</t>
+          <t>matchmaker salt lake city</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>Oklahoma City (1.4M metro) — links up to the Oklahoma City location page.</t>
+          <t>Salt Lake City (1.2M metro) — links up to the Salt Lake City location page.</t>
         </is>
       </c>
     </row>
@@ -5484,19 +5484,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A Memphis Matchmaker's Approach to Intentional Dating</t>
+          <t>Looking for a Matchmaker in Naples? Here's How to Choose</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>matchmaker memphis</t>
+          <t>naples matchmaker</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>Memphis (1.3M metro) — links up to the Memphis location page.</t>
+          <t>Naples (0.38M metro) — links up to the Naples location page.</t>
         </is>
       </c>
     </row>
@@ -5533,19 +5533,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Is a Richmond Matchmaker Worth It? An Honest Take</t>
+          <t>Beverly Hills Matchmaker: Discreet, High-End Introductions</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>richmond matchmaker</t>
+          <t>beverly hills matchmaker</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>Richmond (1.3M metro) — links up to the Richmond location page.</t>
+          <t>Beverly Hills (affluent enclave) — links up to the Los Angeles metro.</t>
         </is>
       </c>
     </row>
@@ -5582,19 +5582,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A New Orleans Matchmaker's Approach to Intentional Dating</t>
+          <t>Looking for a Matchmaker in Malibu?</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>new orleans matchmaker</t>
+          <t>malibu matchmaker</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>New Orleans (1.3M metro) — links up to the New Orleans location page.</t>
+          <t>Malibu (affluent enclave) — links up to the Los Angeles metro.</t>
         </is>
       </c>
     </row>
@@ -5631,19 +5631,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Professional Matchmaking in Salt Lake City: What to Expect</t>
+          <t>Your Personal Matchmaker in Newport Beach</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>matchmaker salt lake city</t>
+          <t>newport beach matchmaker</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Salt Lake City (1.2M metro) — links up to the Salt Lake City location page.</t>
+          <t>Newport Beach (affluent enclave) — links up to the Los Angeles metro / California state.</t>
         </is>
       </c>
     </row>
@@ -5680,19 +5680,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Naples? Here's How to Choose</t>
+          <t>San Jose Matchmaking for Discerning Singles</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>naples matchmaker</t>
+          <t>matchmaker san jose</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>Naples (0.38M metro) — links up to the Naples location page.</t>
+          <t>San Jose (affluent enclave) — links up to the San Francisco / Bay Area metro.</t>
         </is>
       </c>
     </row>
@@ -5729,19 +5729,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beverly Hills Matchmaker: Discreet, High-End Introductions</t>
+          <t>How to Find a Matchmaker in Palo Alto You Can Trust</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>beverly hills matchmaker</t>
+          <t>palo alto matchmaker</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>Beverly Hills (affluent enclave) — links up to the Los Angeles metro.</t>
+          <t>Palo Alto (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in Malibu?</t>
+          <t>The Atherton Matchmaker for Marriage-Minded Singles</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>malibu matchmaker</t>
+          <t>atherton matchmaker</t>
         </is>
       </c>
       <c r="D107" s="4" t="n">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>Malibu (affluent enclave) — links up to the Los Angeles metro.</t>
+          <t>Atherton (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Newport Beach</t>
+          <t>Meet Your Match With a Hillsborough Matchmaker</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>newport beach matchmaker</t>
+          <t>hillsborough matchmaker</t>
         </is>
       </c>
       <c r="D108" s="4" t="n">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>Newport Beach (affluent enclave) — links up to the Los Angeles metro / California state.</t>
+          <t>Hillsborough (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -5876,19 +5876,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>San Jose Matchmaking for Discerning Singles</t>
+          <t>Elite Matchmaking in Los Altos, Done for You</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>matchmaker san jose</t>
+          <t>los altos matchmaker</t>
         </is>
       </c>
       <c r="D109" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>San Jose (affluent enclave) — links up to the San Francisco / Bay Area metro.</t>
+          <t>Los Altos (affluent enclave) — links up to the San Francisco metro.</t>
         </is>
       </c>
     </row>
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>How to Find a Matchmaker in Palo Alto You Can Trust</t>
+          <t>Scarsdale Matchmaker: Discreet, High-End Introductions</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>palo alto matchmaker</t>
+          <t>scarsdale matchmaker</t>
         </is>
       </c>
       <c r="D110" s="4" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>Palo Alto (affluent enclave) — links up to the San Francisco metro.</t>
+          <t>Scarsdale (affluent enclave) — links up to the New York metro.</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Atherton Matchmaker for Marriage-Minded Singles</t>
+          <t>Looking for a Matchmaker in the Hamptons?</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>atherton matchmaker</t>
+          <t>hamptons matchmaker</t>
         </is>
       </c>
       <c r="D111" s="4" t="n">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>Atherton (affluent enclave) — links up to the San Francisco metro.</t>
+          <t>Hamptons (affluent enclave) — links up to the New York metro.</t>
         </is>
       </c>
     </row>
@@ -6023,12 +6023,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Meet Your Match With a Hillsborough Matchmaker</t>
+          <t>Your Personal Matchmaker in Greenwich</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>hillsborough matchmaker</t>
+          <t>greenwich matchmaker</t>
         </is>
       </c>
       <c r="D112" s="4" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>Hillsborough (affluent enclave) — links up to the San Francisco metro.</t>
+          <t>Greenwich (affluent enclave) — links up to the New York metro / Connecticut state.</t>
         </is>
       </c>
     </row>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Elite Matchmaking in Los Altos, Done for You</t>
+          <t>Darien Matchmaking for Discerning Singles</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>los altos matchmaker</t>
+          <t>darien matchmaker</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>Los Altos (affluent enclave) — links up to the San Francisco metro.</t>
+          <t>Darien (affluent enclave) — links up to the New York metro / Connecticut state.</t>
         </is>
       </c>
     </row>
@@ -6121,12 +6121,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Scarsdale Matchmaker: Discreet, High-End Introductions</t>
+          <t>How to Find a Matchmaker in Short Hills You Can Trust</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>scarsdale matchmaker</t>
+          <t>short hills matchmaker</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>Scarsdale (affluent enclave) — links up to the New York metro.</t>
+          <t>Short Hills (affluent enclave) — links up to the New York metro / New Jersey state.</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Looking for a Matchmaker in the Hamptons?</t>
+          <t>The McLean Matchmaker for Marriage-Minded Singles</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>hamptons matchmaker</t>
+          <t>mclean matchmaker</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Hamptons (affluent enclave) — links up to the New York metro.</t>
+          <t>McLean (affluent enclave) — links up to the Washington DC metro / Virginia state.</t>
         </is>
       </c>
     </row>
@@ -6219,12 +6219,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Your Personal Matchmaker in Greenwich</t>
+          <t>Meet Your Match With a Boca Raton Matchmaker</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>greenwich matchmaker</t>
+          <t>boca raton matchmaker</t>
         </is>
       </c>
       <c r="D116" s="4" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Greenwich (affluent enclave) — links up to the New York metro / Connecticut state.</t>
+          <t>Boca Raton (affluent enclave) — links up to the Miami metro / Florida state.</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Darien Matchmaking for Discerning Singles</t>
+          <t>Elite Matchmaking in Park City, Done for You</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>darien matchmaker</t>
+          <t>park city matchmaker</t>
         </is>
       </c>
       <c r="D117" s="4" t="n">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Darien (affluent enclave) — links up to the New York metro / Connecticut state.</t>
+          <t>Park City (affluent enclave) — links up to the Salt Lake City metro / Utah state.</t>
         </is>
       </c>
     </row>
@@ -6317,12 +6317,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>How to Find a Matchmaker in Short Hills You Can Trust</t>
+          <t>Highland Park, TX Matchmaker: Discreet, High-End Introductions</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>short hills matchmaker</t>
+          <t>highland park matchmaker</t>
         </is>
       </c>
       <c r="D118" s="4" t="n">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>Short Hills (affluent enclave) — links up to the New York metro / New Jersey state.</t>
+          <t>Highland Park, TX (affluent suburb) — links up to the Dallas metro.</t>
         </is>
       </c>
     </row>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>The McLean Matchmaker for Marriage-Minded Singles</t>
+          <t>Looking for a Matchmaker in Southlake, TX?</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>mclean matchmaker</t>
+          <t>southlake matchmaker</t>
         </is>
       </c>
       <c r="D119" s="4" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>McLean (affluent enclave) — links up to the Washington DC metro / Virginia state.</t>
+          <t>Southlake, TX (affluent suburb) — links up to the Dallas metro.</t>
         </is>
       </c>
     </row>
@@ -6415,12 +6415,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Meet Your Match With a Boca Raton Matchmaker</t>
+          <t>Your Personal Matchmaker in Great Falls, VA</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>boca raton matchmaker</t>
+          <t>great falls matchmaker</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Boca Raton (affluent enclave) — links up to the Miami metro / Florida state.</t>
+          <t>Great Falls, VA (affluent suburb) — links up to the Washington DC metro / Virginia state.</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Elite Matchmaking in Park City, Done for You</t>
+          <t>Hinsdale, IL Matchmaking for Discerning Singles</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>park city matchmaker</t>
+          <t>hinsdale matchmaker</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>Park City (affluent enclave) — links up to the Salt Lake City metro / Utah state.</t>
+          <t>Hinsdale, IL (affluent suburb) — links up to the Chicago metro.</t>
         </is>
       </c>
     </row>
@@ -22410,18 +22410,18 @@
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
         <is>
-          <t>sacramento matchmaker</t>
+          <t>pittsburgh matchmaker</t>
         </is>
       </c>
       <c r="B482" s="4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C482" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D482" s="10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>29</v>
+      </c>
+      <c r="D482" s="9" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E482" s="6" t="inlineStr">
@@ -22443,18 +22443,18 @@
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
         <is>
-          <t>pittsburgh matchmaker</t>
+          <t>las vegas matchmaker</t>
         </is>
       </c>
       <c r="B483" s="4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="C483" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D483" s="9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>15</v>
+      </c>
+      <c r="D483" s="10" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="E483" s="6" t="inlineStr">
@@ -22476,7 +22476,7 @@
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
         <is>
-          <t>las vegas matchmaker</t>
+          <t>kansas city matchmaker</t>
         </is>
       </c>
       <c r="B484" s="4" t="n">
@@ -22509,14 +22509,14 @@
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>kansas city matchmaker</t>
+          <t>matchmaker columbus ohio</t>
         </is>
       </c>
       <c r="B485" s="4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C485" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D485" s="10" t="inlineStr">
         <is>
@@ -22542,14 +22542,14 @@
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>matchmaker columbus ohio</t>
+          <t>indianapolis matchmaker</t>
         </is>
       </c>
       <c r="B486" s="4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C486" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D486" s="10" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
         <is>
-          <t>indianapolis matchmaker</t>
+          <t>nashville matchmaker</t>
         </is>
       </c>
       <c r="B487" s="4" t="n">
@@ -22608,7 +22608,7 @@
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>nashville matchmaker</t>
+          <t>jacksonville matchmaker</t>
         </is>
       </c>
       <c r="B488" s="4" t="n">
@@ -22641,7 +22641,7 @@
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
         <is>
-          <t>jacksonville matchmaker</t>
+          <t>richmond matchmaker</t>
         </is>
       </c>
       <c r="B489" s="4" t="n">
@@ -22674,14 +22674,14 @@
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>oklahoma city matchmaker</t>
+          <t>matchmaker salt lake city</t>
         </is>
       </c>
       <c r="B490" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C490" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D490" s="10" t="inlineStr">
         <is>
@@ -22707,14 +22707,14 @@
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
         <is>
-          <t>matchmaker memphis</t>
+          <t>naples matchmaker</t>
         </is>
       </c>
       <c r="B491" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C491" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D491" s="10" t="inlineStr">
         <is>
@@ -22740,14 +22740,14 @@
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>richmond matchmaker</t>
+          <t>beverly hills matchmaker</t>
         </is>
       </c>
       <c r="B492" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C492" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D492" s="10" t="inlineStr">
         <is>
@@ -22773,14 +22773,14 @@
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
         <is>
-          <t>new orleans matchmaker</t>
+          <t>malibu matchmaker</t>
         </is>
       </c>
       <c r="B493" s="4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C493" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D493" s="10" t="inlineStr">
         <is>
@@ -22806,14 +22806,14 @@
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>matchmaker salt lake city</t>
+          <t>newport beach matchmaker</t>
         </is>
       </c>
       <c r="B494" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C494" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D494" s="10" t="inlineStr">
         <is>
@@ -22839,14 +22839,14 @@
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
         <is>
-          <t>naples matchmaker</t>
+          <t>matchmaker san jose</t>
         </is>
       </c>
       <c r="B495" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C495" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D495" s="10" t="inlineStr">
         <is>
@@ -22872,14 +22872,14 @@
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>beverly hills matchmaker</t>
+          <t>palo alto matchmaker</t>
         </is>
       </c>
       <c r="B496" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C496" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D496" s="10" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
         <is>
-          <t>malibu matchmaker</t>
+          <t>atherton matchmaker</t>
         </is>
       </c>
       <c r="B497" s="4" t="n">
@@ -22938,7 +22938,7 @@
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
         <is>
-          <t>newport beach matchmaker</t>
+          <t>hillsborough matchmaker</t>
         </is>
       </c>
       <c r="B498" s="4" t="n">
@@ -22971,14 +22971,14 @@
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
         <is>
-          <t>matchmaker san jose</t>
+          <t>los altos matchmaker</t>
         </is>
       </c>
       <c r="B499" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C499" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D499" s="10" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>palo alto matchmaker</t>
+          <t>scarsdale matchmaker</t>
         </is>
       </c>
       <c r="B500" s="4" t="n">
@@ -23037,7 +23037,7 @@
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
         <is>
-          <t>atherton matchmaker</t>
+          <t>hamptons matchmaker</t>
         </is>
       </c>
       <c r="B501" s="4" t="n">
@@ -23070,7 +23070,7 @@
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
         <is>
-          <t>hillsborough matchmaker</t>
+          <t>greenwich matchmaker</t>
         </is>
       </c>
       <c r="B502" s="4" t="n">
@@ -23103,7 +23103,7 @@
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
         <is>
-          <t>los altos matchmaker</t>
+          <t>darien matchmaker</t>
         </is>
       </c>
       <c r="B503" s="4" t="n">
@@ -23136,7 +23136,7 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>scarsdale matchmaker</t>
+          <t>short hills matchmaker</t>
         </is>
       </c>
       <c r="B504" s="4" t="n">
@@ -23169,7 +23169,7 @@
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
         <is>
-          <t>hamptons matchmaker</t>
+          <t>mclean matchmaker</t>
         </is>
       </c>
       <c r="B505" s="4" t="n">
@@ -23202,7 +23202,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>greenwich matchmaker</t>
+          <t>boca raton matchmaker</t>
         </is>
       </c>
       <c r="B506" s="4" t="n">
@@ -23235,7 +23235,7 @@
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>darien matchmaker</t>
+          <t>park city matchmaker</t>
         </is>
       </c>
       <c r="B507" s="4" t="n">
@@ -23268,7 +23268,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>short hills matchmaker</t>
+          <t>highland park matchmaker</t>
         </is>
       </c>
       <c r="B508" s="4" t="n">
@@ -23301,7 +23301,7 @@
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>mclean matchmaker</t>
+          <t>southlake matchmaker</t>
         </is>
       </c>
       <c r="B509" s="4" t="n">
@@ -23334,7 +23334,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>boca raton matchmaker</t>
+          <t>great falls matchmaker</t>
         </is>
       </c>
       <c r="B510" s="4" t="n">
@@ -23367,7 +23367,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>park city matchmaker</t>
+          <t>hinsdale matchmaker</t>
         </is>
       </c>
       <c r="B511" s="4" t="n">
@@ -23930,9 +23930,9 @@
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">  120 articles, split exactly 40/40/40 across Months 1-3
-  36,870 total monthly searches addressed
+  36,700 total monthly searches addressed
   114 easy wins at KD &lt; 30 — front-loaded into Month 1 so you see local rankings early
-  Average difficulty KD 16.0 — deliberately achievable, weighted toward winnable local terms</t>
+  Average difficulty KD 16.3 — deliberately achievable, weighted toward winnable local terms</t>
         </is>
       </c>
     </row>

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>It's Just Lunch Reviews</t>
+          <t>It's Just Lunch Reviews (2026)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How Much Does Tawkify Cost?</t>
+          <t>How Much Does Tawkify Cost in 2026?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luma Matchmaking: An Honest Review</t>
+          <t>Luma Matchmaking: An Honest Review (2026)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>How Much Does It's Just Lunch Cost?</t>
+          <t>How Much Does It's Just Lunch Cost in 2026?</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Three Day Rule Reviews</t>
+          <t>Three Day Rule Reviews (2026)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Matchmaking Company Reviews</t>
+          <t>The Matchmaking Company Reviews (2026)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Best Alternatives to Dating Apps</t>
+          <t>The Best Alternatives to Dating Apps (2026)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What Drives the Cost of Matchmaking Services</t>
+          <t>What Drives the Cost of Matchmaking Services (2026)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Selective Search: A Matchmaking Review</t>
+          <t>Selective Search: A Matchmaking Review (2026)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Best High-End Matchmaking Services</t>
+          <t>Best High-End Matchmaking Services (2026)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Best Elite Matchmaking Services</t>
+          <t>Best Elite Matchmaking Services (2026)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Top Matchmaking Services, Compared</t>
+          <t>Top Matchmaking Services, Compared (2026)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Best Matchmakers in New York City</t>
+          <t>Best Matchmakers in New York City (2026)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Best Luxury Matchmaking Services</t>
+          <t>Best Luxury Matchmaking Services (2026)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kelleher International Reviews</t>
+          <t>Kelleher International Reviews (2026)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>How Much Does Three Day Rule Cost?</t>
+          <t>How Much Does Three Day Rule Cost in 2026?</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Professional Matchmaker Cost</t>
+          <t>Professional Matchmaker Cost (2026)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Los Angeles</t>
+          <t>Best Matchmakers in Los Angeles (2026)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Florida</t>
+          <t>Best Matchmakers in Florida (2026)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Miami</t>
+          <t>Best Matchmakers in Miami (2026)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Chicago</t>
+          <t>Best Matchmakers in Chicago (2026)</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Dallas</t>
+          <t>Best Matchmakers in Dallas (2026)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Washington, DC</t>
+          <t>Best Matchmakers in Washington, DC (2026)</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Atlanta</t>
+          <t>Best Matchmakers in Atlanta (2026)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Best Matchmakers in Boston</t>
+          <t>Best Matchmakers in Boston (2026)</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Best Matchmakers in the San Francisco Bay Area</t>
+          <t>Best Matchmakers in the San Francisco Bay Area (2026)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Best Matchmakers for Professionals</t>
+          <t>Best Matchmakers for Professionals (2026)</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tawkify Alternatives Worth Considering</t>
+          <t>Tawkify Alternatives Worth Considering (2026)</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>It's Just Lunch Alternatives</t>
+          <t>It's Just Lunch Alternatives (2026)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tawkify vs It's Just Lunch</t>
+          <t>Tawkify vs It's Just Lunch (2026)</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>It's Just Lunch vs a High-Touch Matchmaker</t>
+          <t>It's Just Lunch vs a High-Touch Matchmaker (2026)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kelleher vs Selective Search: Elite Matchmaking Compared</t>
+          <t>Kelleher vs Selective Search: Elite Matchmaking Compared (2026)</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Elite Matchmaking Services, Compared</t>
+          <t>Elite Matchmaking Services, Compared (2026)</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Matchmaker Fees, Explained</t>
+          <t>Matchmaker Fees, Explained (2026)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Matchmaking Service Prices: What You'll Pay</t>
+          <t>Matchmaking Service Prices: What You'll Pay (2026)</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>How Much Does a Personal Matchmaker Cost?</t>
+          <t>How Much Does a Personal Matchmaker Cost in 2026?</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>High-End Matchmaking: What the Price Includes</t>
+          <t>High-End Matchmaking: What the Price Includes (2026)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Matchmaker Cost by Tier: Budget to Elite</t>
+          <t>Matchmaker Cost by Tier: Budget to Elite (2026)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">

--- a/decks/master-matchmakers/keyword-research.xlsx
+++ b/decks/master-matchmakers/keyword-research.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luma Matchmaking: An Honest Review (2026)</t>
+          <t>Luma Matchmaking Reviews &amp; Alternatives (2026)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Three Day Rule Reviews (2026)</t>
+          <t>Three Day Rule Reviews &amp; Alternatives (2026)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Matchmaking Company Reviews (2026)</t>
+          <t>The Matchmaking Company Reviews &amp; Alternatives (2026)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Selective Search: A Matchmaking Review (2026)</t>
+          <t>Selective Search Reviews &amp; Alternatives (2026)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kelleher International Reviews (2026)</t>
+          <t>Kelleher International Reviews &amp; Alternatives (2026)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
